--- a/files/港岛-鸭脷洲-凯玥.xlsx
+++ b/files/港岛-鸭脷洲-凯玥.xlsx
@@ -8,12 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座 销控表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座 销控表" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座 销控表" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6座 销控表" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8座 销控表" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -116,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -181,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -197,51 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1163,7 +1019,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1209,7 +1065,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1255,7 +1111,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1351,7 +1207,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1397,7 +1253,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1493,7 +1349,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1539,7 +1395,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1585,7 +1441,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1631,7 +1487,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -1677,7 +1533,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -1723,7 +1579,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -1769,7 +1625,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -1815,7 +1671,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -1861,7 +1717,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -1907,7 +1763,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -1953,7 +1809,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -1999,7 +1855,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2045,7 +1901,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2091,7 +1947,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2137,7 +1993,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2183,7 +2039,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2229,7 +2085,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2275,7 +2131,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2321,7 +2177,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2367,7 +2223,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -2413,7 +2269,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -2459,7 +2315,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -2505,7 +2361,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -2551,7 +2407,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -2597,7 +2453,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -2643,7 +2499,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -2689,7 +2545,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-12</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3481,7 +3337,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -3527,7 +3383,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -3573,7 +3429,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -3669,7 +3525,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -3715,7 +3571,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -3761,7 +3617,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -3857,7 +3713,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -3903,7 +3759,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -3949,7 +3805,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -3995,7 +3851,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -4041,7 +3897,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -4087,7 +3943,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -4133,7 +3989,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -4229,7 +4085,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -4325,7 +4181,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-17</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -4371,7 +4227,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-16</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -4417,7 +4273,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -4463,7 +4319,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -4509,7 +4365,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -4555,7 +4411,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -4601,7 +4457,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -4697,7 +4553,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -4793,7 +4649,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -4839,7 +4695,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -4885,7 +4741,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -4931,7 +4787,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -5477,7 +5333,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-18</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -6573,7 +6429,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-02-13</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -6669,7 +6525,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -6715,7 +6571,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-01-26</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -6761,7 +6617,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-12-14</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -6857,7 +6713,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -6903,7 +6759,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -7099,7 +6955,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -8045,7 +7901,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-01-21</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -8791,7 +8647,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -8987,7 +8843,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -9083,7 +8939,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -9129,7 +8985,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -9175,7 +9031,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -9221,7 +9077,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -9267,7 +9123,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -9363,7 +9219,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -9409,7 +9265,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -9505,7 +9361,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -9601,7 +9457,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -10597,7 +10453,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -10693,7 +10549,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -10789,7 +10645,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -10885,7 +10741,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -11031,7 +10887,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -11077,7 +10933,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -11123,7 +10979,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -11169,7 +11025,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -11215,7 +11071,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -11261,7 +11117,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -11307,7 +11163,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -11353,7 +11209,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -11399,7 +11255,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -11445,7 +11301,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -11491,7 +11347,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -11537,7 +11393,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -11583,7 +11439,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -11629,7 +11485,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -11675,7 +11531,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -11721,7 +11577,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -11767,7 +11623,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -11813,7 +11669,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -11859,7 +11715,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -11905,7 +11761,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -11951,7 +11807,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -11997,7 +11853,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -12043,7 +11899,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -12089,7 +11945,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -15011,4103 +14867,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>凯玥 - 1座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>46 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>33 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>5 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>8 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>29&amp;30/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 7396呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 4091呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 1956呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 2247呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 1956呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 2247呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>A | 1956呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>B | 2247呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>A | 1864呎 (4+房)
-$6,080万
-$32,618/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>B | 2247呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>A | 1864呎 (4+房)
-$5,525万
-$29,642/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="inlineStr">
-        <is>
-          <t>B | 2107呎 (4+房)
-$6,572万
-$31,191/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>A | 1864呎 (4+房)
-$5,940万
-$31,866/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 2247呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 1956呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C14" s="19" t="inlineStr">
-        <is>
-          <t>B | 2107呎 (4+房)
-$6,900万
-$32,748/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>A | 1864呎 (4+房)
-$5,408万
-$29,013/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>B | 2107呎 (4+房)
-$6,600万
-$31,324/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>A | 1864呎 (4+房)
-$5,800万
-$31,116/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="inlineStr">
-        <is>
-          <t>B | 2107呎 (4+房)
-$6,792万
-$32,234/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="inlineStr">
-        <is>
-          <t>A | 1864呎 (4+房)
-$5,238万
-$28,101/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="19" t="inlineStr">
-        <is>
-          <t>B | 2107呎 (4+房)
-$6,608万
-$31,362/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="inlineStr">
-        <is>
-          <t>A | 1864呎 (4+房)
-$5,183万
-$27,808/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="19" t="inlineStr">
-        <is>
-          <t>B | 2107呎 (4+房)
-$6,446万
-$30,591/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="inlineStr">
-        <is>
-          <t>A | 1864呎 (4+房)
-$5,561万
-$29,835/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="19" t="inlineStr">
-        <is>
-          <t>B | 2108呎 (4+房)
-$6,189万
-$29,358/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
-        <is>
-          <t>A | 1864呎 (4+房)
-$5,548万
-$29,765/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="19" t="inlineStr">
-        <is>
-          <t>B | 2108呎 (4+房)
-$6,287万
-$29,825/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr">
-        <is>
-          <t>A | 1864呎 (4+房)
-$5,086万
-$27,283/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C21" s="19" t="inlineStr">
-        <is>
-          <t>B | 2108呎 (4+房)
-$5,865万
-$27,821/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr">
-        <is>
-          <t>A | 1864呎 (4+房)
-$5,526万
-$29,645/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="19" t="inlineStr">
-        <is>
-          <t>B | 2108呎 (4+房)
-$5,865万
-$27,821/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B23" s="19" t="inlineStr">
-        <is>
-          <t>A | 1864呎 (4+房)
-$5,546万
-$29,756/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C23" s="19" t="inlineStr">
-        <is>
-          <t>B | 2108呎 (4+房)
-$6,297万
-$29,873/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B24" s="19" t="inlineStr">
-        <is>
-          <t>A | 1864呎 (4+房)
-$5,546万
-$29,756/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C24" s="19" t="inlineStr">
-        <is>
-          <t>B | 2108呎 (4+房)
-$6,297万
-$29,873/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B25" s="19" t="inlineStr">
-        <is>
-          <t>A | 1864呎 (4+房)
-$5,178万
-$27,778/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C25" s="19" t="inlineStr">
-        <is>
-          <t>B | 2108呎 (4+房)
-$6,448万
-$30,588/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B26" s="19" t="inlineStr">
-        <is>
-          <t>A | 1864呎 (4+房)
-$4,920万
-$26,395/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C26" s="19" t="inlineStr">
-        <is>
-          <t>B | 2108呎 (4+房)
-$6,455万
-$30,619/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B27" s="19" t="inlineStr">
-        <is>
-          <t>A | 1864呎 (4+房)
-$5,250万
-$28,165/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C27" s="19" t="inlineStr">
-        <is>
-          <t>B | 2108呎 (4+房)
-$6,046万
-$28,682/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B28" s="19" t="inlineStr">
-        <is>
-          <t>A | 1864呎 (4+房)
-$5,380万
-$28,863/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C28" s="19" t="inlineStr">
-        <is>
-          <t>B | 2108呎 (4+房)
-$5,540万
-$26,281/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>A | 1889呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>B | 2179呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>凯玥 - 2座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>46 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>26 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>20 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>29&amp;30/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 8368呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 4559呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 2236呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 2604呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 2236呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 2604呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 2236呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 2604呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 2236呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 2604呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 2236呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 2604呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>A | 2137呎 (4+房)
-$7,094万
-$33,196/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
-        <is>
-          <t>B | 2464呎 (4+房)
-$8,494万
-$34,472/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 2236呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="19" t="inlineStr">
-        <is>
-          <t>B | 2464呎 (4+房)
-$7,994万
-$32,444/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>A | 2137呎 (4+房)
-$6,582万
-$30,799/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>B | 2464呎 (4+房)
-$8,200万
-$33,279/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 2236呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="inlineStr">
-        <is>
-          <t>B | 2464呎 (4+房)
-$8,200万
-$33,279/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="inlineStr">
-        <is>
-          <t>A | 2137呎 (4+房)
-$6,526万
-$30,540/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="19" t="inlineStr">
-        <is>
-          <t>B | 2464呎 (4+房)
-$8,101万
-$32,876/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="inlineStr">
-        <is>
-          <t>A | 2137呎 (4+房)
-$6,526万
-$30,540/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="19" t="inlineStr">
-        <is>
-          <t>B | 2464呎 (4+房)
-$8,101万
-$32,876/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="inlineStr">
-        <is>
-          <t>A | 2137呎 (4+房)
-$6,526万
-$30,540/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="19" t="inlineStr">
-        <is>
-          <t>B | 2604呎 (4+房)
-$8,101万
-$31,108/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>A | 2236呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="19" t="inlineStr">
-        <is>
-          <t>B | 2464呎 (4+房)
-$8,333万
-$33,818/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>A | 2236呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C21" s="19" t="inlineStr">
-        <is>
-          <t>B | 2464呎 (4+房)
-$8,122万
-$32,961/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr">
-        <is>
-          <t>A | 2137呎 (4+房)
-$6,525万
-$30,536/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="19" t="inlineStr">
-        <is>
-          <t>B | 2464呎 (4+房)
-$8,075万
-$32,770/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B23" s="19" t="inlineStr">
-        <is>
-          <t>A | 2137呎 (4+房)
-$6,478万
-$30,314/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C23" s="19" t="inlineStr">
-        <is>
-          <t>B | 2464呎 (4+房)
-$7,900万
-$32,062/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B24" s="19" t="inlineStr">
-        <is>
-          <t>A | 2137呎 (4+房)
-$7,163万
-$33,520/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C24" s="19" t="inlineStr">
-        <is>
-          <t>B | 2464呎 (4+房)
-$7,900万
-$32,062/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>A | 2236呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C25" s="19" t="inlineStr">
-        <is>
-          <t>B | 2464呎 (4+房)
-$8,100万
-$32,873/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>A | 2236呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C26" s="19" t="inlineStr">
-        <is>
-          <t>B | 2464呎 (4+房)
-$7,853万
-$31,870/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B27" s="19" t="inlineStr">
-        <is>
-          <t>A | 2137呎 (4+房)
-$7,096万
-$33,206/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C27" s="19" t="inlineStr">
-        <is>
-          <t>B | 2464呎 (4+房)
-$8,251万
-$33,485/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B28" s="19" t="inlineStr">
-        <is>
-          <t>A | 2137呎 (4+房)
-$6,723万
-$31,461/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C28" s="19" t="inlineStr">
-        <is>
-          <t>B | 2464呎 (4+房)
-$7,830万
-$31,776/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>A | 2169呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>B | 2531呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>凯玥 - 3座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>48 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>8 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>8 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>5 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>27 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>29&amp;30/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 9663呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 6297呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 3317呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 3635呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 3317呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 3635呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 3317呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 3635呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 3317呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="19" t="inlineStr">
-        <is>
-          <t>B | 3635呎 (4+房)
-$18,466万
-$50,800/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 3317呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 3635呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 3316呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 3627呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 3316呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 3627呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 3316呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>B | 3627呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 3316呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 3627呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 3316呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 3627呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 3316呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 3627呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>A | 3316呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 3627呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 3316呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 3627呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 3316呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>B | 3627呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>A | 3316呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C22" s="19" t="inlineStr">
-        <is>
-          <t>B | 3627呎 (4+房)
-$18,328万
-$50,531/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B23" s="19" t="inlineStr">
-        <is>
-          <t>A | 3207呎 (4+房)
-$16,417万
-$51,191/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C23" s="19" t="inlineStr">
-        <is>
-          <t>B | 3477呎 (4+房)
-$14,008万
-$40,288/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B24" s="20" t="inlineStr">
-        <is>
-          <t>A | 3316呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C24" s="19" t="inlineStr">
-        <is>
-          <t>B | 3477呎 (4+房)
-$17,228万
-$49,549/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B25" s="19" t="inlineStr">
-        <is>
-          <t>A | 3207呎 (4+房)
-$12,106万
-$37,749/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C25" s="19" t="inlineStr">
-        <is>
-          <t>B | 3627呎 (4+房)
-$13,194万
-$36,379/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B26" s="20" t="inlineStr">
-        <is>
-          <t>A | 3316呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C26" s="20" t="inlineStr">
-        <is>
-          <t>B | 3627呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B27" s="19" t="inlineStr">
-        <is>
-          <t>A | 3207呎 (4+房)
-$12,066万
-$37,625/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C27" s="20" t="inlineStr">
-        <is>
-          <t>B | 3627呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B28" s="20" t="inlineStr">
-        <is>
-          <t>A | 3316呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C28" s="20" t="inlineStr">
-        <is>
-          <t>B | 3627呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B29" s="20" t="inlineStr">
-        <is>
-          <t>A | 3316呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C29" s="20" t="inlineStr">
-        <is>
-          <t>B | 3627呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>A | 3316呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>B | 3627呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>凯玥 - 5座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>48 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>4 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>12 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>12 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>20 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>29&amp;30/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 6866呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 3846呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 2310呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 1944呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 2310呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 1944呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 2310呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 1944呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 2310呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 1944呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 2310呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 1944呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 2310呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
-        <is>
-          <t>B | 1824呎 (4+房)
-$7,582万
-$41,566/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 2310呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 1944呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 2310呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 1944呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 2310呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 1944呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 2310呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 1944呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 2310呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 1944呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 2310呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>B | 1944呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
-        <is>
-          <t>A | 2178呎 (4+房)
-$7,339万
-$33,695/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 1944呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 2310呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>B | 1944呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr">
-        <is>
-          <t>A | 2178呎 (4+房)
-$6,745万
-$30,970/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>B | 1944呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B23" s="19" t="inlineStr">
-        <is>
-          <t>A | 2178呎 (4+房)
-$7,251万
-$33,290/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>B | 1944呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B24" s="19" t="inlineStr">
-        <is>
-          <t>A | 2178呎 (4+房)
-$6,956万
-$31,937/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C24" s="19" t="inlineStr">
-        <is>
-          <t>B | 1824呎 (4+房)
-$5,323万
-$29,181/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B25" s="19" t="inlineStr">
-        <is>
-          <t>A | 2178呎 (4+房)
-$6,468万
-$29,697/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C25" s="19" t="inlineStr">
-        <is>
-          <t>B | 1824呎 (4+房)
-$5,800万
-$31,798/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B26" s="19" t="inlineStr">
-        <is>
-          <t>A | 2178呎 (4+房)
-$6,280万
-$28,834/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C26" s="20" t="inlineStr">
-        <is>
-          <t>B | 1944呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B27" s="20" t="inlineStr">
-        <is>
-          <t>A | 2310呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C27" s="19" t="inlineStr">
-        <is>
-          <t>B | 1824呎 (4+房)
-$5,724万
-$31,379/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B28" s="20" t="inlineStr">
-        <is>
-          <t>A | 2310呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C28" s="19" t="inlineStr">
-        <is>
-          <t>B | 1824呎 (4+房)
-$5,953万
-$32,634/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B29" s="20" t="inlineStr">
-        <is>
-          <t>A | 2310呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C29" s="19" t="inlineStr">
-        <is>
-          <t>B | 1824呎 (4+房)
-$5,724万
-$31,379/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>A | 2310呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>B | 1944呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>凯玥 - 6座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>51 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>28 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>11 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>12 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 3184呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 1696呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 1689呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 1696呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 1689呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 1697呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 1689呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 1697呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 1689呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 1697呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>B | 1689呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 1697呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 1689呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 1697呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 1689呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>A | 1626呎 (4+房)
-$4,910万
-$30,197/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 1689呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>A | 1626呎 (4+房)
-$4,768万
-$29,323/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 1689呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>A | 1626呎 (4+房)
-$4,768万
-$29,323/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 1689呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="inlineStr">
-        <is>
-          <t>A | 1626呎 (4+房)
-$4,378万
-$26,927/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 1689呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 1697呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>B | 1689呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="inlineStr">
-        <is>
-          <t>A | 1626呎 (4+房)
-$4,242万
-$26,092/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="19" t="inlineStr">
-        <is>
-          <t>B | 1619呎 (4+房)
-$4,206万
-$25,977/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
-        <is>
-          <t>A | 1626呎 (4+房)
-$4,209万
-$25,883/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="19" t="inlineStr">
-        <is>
-          <t>B | 1619呎 (4+房)
-$4,189万
-$25,872/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr">
-        <is>
-          <t>A | 1626呎 (4+房)
-$4,124万
-$25,361/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C21" s="19" t="inlineStr">
-        <is>
-          <t>B | 1619呎 (4+房)
-$4,504万
-$27,821/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr">
-        <is>
-          <t>A | 1626呎 (4+房)
-$4,592万
-$28,239/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="19" t="inlineStr">
-        <is>
-          <t>B | 1619呎 (4+房)
-$4,172万
-$25,768/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B23" s="19" t="inlineStr">
-        <is>
-          <t>A | 1626呎 (4+房)
-$4,158万
-$25,570/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C23" s="19" t="inlineStr">
-        <is>
-          <t>B | 1619呎 (4+房)
-$4,155万
-$25,664/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B24" s="19" t="inlineStr">
-        <is>
-          <t>A | 1626呎 (4+房)
-$4,200万
-$25,830/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C24" s="19" t="inlineStr">
-        <is>
-          <t>B | 1619呎 (4+房)
-$4,238万
-$26,177/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B25" s="19" t="inlineStr">
-        <is>
-          <t>A | 1626呎 (4+房)
-$4,158万
-$25,570/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C25" s="19" t="inlineStr">
-        <is>
-          <t>B | 1619呎 (4+房)
-$4,200万
-$25,942/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B26" s="19" t="inlineStr">
-        <is>
-          <t>A | 1626呎 (4+房)
-$4,141万
-$25,465/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C26" s="19" t="inlineStr">
-        <is>
-          <t>B | 1619呎 (4+房)
-$4,316万
-$26,660/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B27" s="19" t="inlineStr">
-        <is>
-          <t>A | 1626呎 (4+房)
-$4,523万
-$27,815/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C27" s="19" t="inlineStr">
-        <is>
-          <t>B | 1619呎 (4+房)
-$4,150万
-$25,633/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B28" s="19" t="inlineStr">
-        <is>
-          <t>A | 1626呎 (4+房)
-$4,163万
-$25,601/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C28" s="19" t="inlineStr">
-        <is>
-          <t>B | 1619呎 (4+房)
-$4,750万
-$29,339/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B29" s="19" t="inlineStr">
-        <is>
-          <t>A | 1626呎 (4+房)
-$4,209万
-$25,883/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C29" s="19" t="inlineStr">
-        <is>
-          <t>B | 1619呎 (4+房)
-$4,273万
-$26,394/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B30" s="19" t="inlineStr">
-        <is>
-          <t>A | 1626呎 (4+房)
-$4,327万
-$26,613/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C30" s="19" t="inlineStr">
-        <is>
-          <t>B | 1619呎 (4+房)
-$4,950万
-$30,574/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>A | 1697呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>B | 1689呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>凯玥 - 8座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>56 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>56 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>B | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>A | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>A | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>B | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>A | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>A | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>B | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>A | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>B | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>A | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>B | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>A | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>B | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>A | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>B | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>A | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>B | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>A | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>B | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>A | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>B | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>A | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>B | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>A | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>B | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
-        <is>
-          <t>A | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>B | 1393呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="inlineStr">
-        <is>
-          <t>A | 1340呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C33" s="16" t="inlineStr">
-        <is>
-          <t>B | 1340呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/港岛-鸭脷洲-凯玥.xlsx
+++ b/files/港岛-鸭脷洲-凯玥.xlsx
@@ -8,6 +8,12 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6座" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8座" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +25,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +47,102 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +153,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +234,63 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +667,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -14867,4 +15060,4103 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>29&amp;30</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 7396呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 4091呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 1956呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 2247呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 1956呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 2247呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 1956呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 2247呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>A | 1864呎 (4+房)
+$6080万
+$32,618/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 2247呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>A | 1864呎 (4+房)
+$5525万
+$29,642/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>B | 2107呎 (4+房)
+$6572万
+$31,191/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>A | 1864呎 (4+房)
+$5940万
+$31,866/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 2247呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 1956呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>B | 2107呎 (4+房)
+$6900万
+$32,748/呎
+(24年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>A | 1864呎 (4+房)
+$5408万
+$29,013/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>B | 2107呎 (4+房)
+$6600万
+$31,324/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>A | 1864呎 (4+房)
+$5800万
+$31,116/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>B | 2107呎 (4+房)
+$6792万
+$32,234/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>A | 1864呎 (4+房)
+$5238万
+$28,101/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>B | 2107呎 (4+房)
+$6608万
+$31,362/呎
+(24年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>A | 1864呎 (4+房)
+$5183万
+$27,808/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>B | 2107呎 (4+房)
+$6446万
+$30,591/呎
+(24年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>A | 1864呎 (4+房)
+$5561万
+$29,835/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>B | 2108呎 (4+房)
+$6189万
+$29,358/呎
+(24年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>A | 1864呎 (4+房)
+$5548万
+$29,765/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>B | 2108呎 (4+房)
+$6287万
+$29,825/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>A | 1864呎 (4+房)
+$5086万
+$27,283/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>B | 2108呎 (4+房)
+$5865万
+$27,821/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>A | 1864呎 (4+房)
+$5526万
+$29,645/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>B | 2108呎 (4+房)
+$5865万
+$27,821/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>A | 1864呎 (4+房)
+$5546万
+$29,756/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="inlineStr">
+        <is>
+          <t>B | 2108呎 (4+房)
+$6297万
+$29,873/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>A | 1864呎 (4+房)
+$5546万
+$29,756/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t>B | 2108呎 (4+房)
+$6297万
+$29,873/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>A | 1864呎 (4+房)
+$5178万
+$27,778/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t>B | 2108呎 (4+房)
+$6448万
+$30,588/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>A | 1864呎 (4+房)
+$4920万
+$26,395/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="C25" s="23" t="inlineStr">
+        <is>
+          <t>B | 2108呎 (4+房)
+$6455万
+$30,619/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>A | 1864呎 (4+房)
+$5250万
+$28,165/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="C26" s="23" t="inlineStr">
+        <is>
+          <t>B | 2108呎 (4+房)
+$6046万
+$28,682/呎
+(24年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>A | 1864呎 (4+房)
+$5380万
+$28,863/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C27" s="23" t="inlineStr">
+        <is>
+          <t>B | 2108呎 (4+房)
+$5540万
+$26,281/呎
+(25年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 1889呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>B | 2179呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>29&amp;30</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 8368呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 4559呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 2236呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 2604呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 2236呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 2604呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 2236呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 2604呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 2236呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 2604呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 2236呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 2604呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>A | 2137呎 (4+房)
+$7094万
+$33,196/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>B | 2464呎 (4+房)
+$8494万
+$34,472/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 2236呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>B | 2464呎 (4+房)
+$7994万
+$32,444/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>A | 2137呎 (4+房)
+$6582万
+$30,799/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>B | 2464呎 (4+房)
+$8200万
+$33,279/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 2236呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>B | 2464呎 (4+房)
+$8200万
+$33,279/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>A | 2137呎 (4+房)
+$6526万
+$30,540/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>B | 2464呎 (4+房)
+$8101万
+$32,876/呎
+(25年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>A | 2137呎 (4+房)
+$6526万
+$30,540/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>B | 2464呎 (4+房)
+$8101万
+$32,876/呎
+(25年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>A | 2137呎 (4+房)
+$6526万
+$30,540/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>B | 2604呎 (4+房)
+$8101万
+$31,108/呎
+(25年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 2236呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>B | 2464呎 (4+房)
+$8333万
+$33,818/呎
+(25年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 2236呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>B | 2464呎 (4+房)
+$8122万
+$32,961/呎
+(25年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>A | 2137呎 (4+房)
+$6525万
+$30,536/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>B | 2464呎 (4+房)
+$8075万
+$32,770/呎
+(25年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>A | 2137呎 (4+房)
+$6478万
+$30,314/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="inlineStr">
+        <is>
+          <t>B | 2464呎 (4+房)
+$7900万
+$32,062/呎
+(24年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>A | 2137呎 (4+房)
+$7163万
+$33,520/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t>B | 2464呎 (4+房)
+$7900万
+$32,062/呎
+(24年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 2236呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t>B | 2464呎 (4+房)
+$8100万
+$32,873/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 2236呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C25" s="23" t="inlineStr">
+        <is>
+          <t>B | 2464呎 (4+房)
+$7853万
+$31,870/呎
+(25年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>A | 2137呎 (4+房)
+$7096万
+$33,206/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C26" s="23" t="inlineStr">
+        <is>
+          <t>B | 2464呎 (4+房)
+$8251万
+$33,485/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>A | 2137呎 (4+房)
+$6723万
+$31,461/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C27" s="23" t="inlineStr">
+        <is>
+          <t>B | 2464呎 (4+房)
+$7830万
+$31,776/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 2169呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>B | 2531呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>3座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>29&amp;30</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 9663呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 6297呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 3317呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 3635呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 3317呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 3635呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 3317呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 3635呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 3317呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>B | 3635呎 (4+房)
+$18466万
+$50,800/呎
+(23年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 3317呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 3635呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 3316呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 3627呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 3316呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 3627呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 3316呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 3627呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 3316呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 3627呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 3316呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 3627呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 3316呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 3627呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 3316呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 3627呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 3316呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 3627呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 3316呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 3627呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 3316呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>B | 3627呎 (4+房)
+$18328万
+$50,531/呎
+(23年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>A | 3207呎 (4+房)
+$16417万
+$51,191/呎
+(23年-01月)</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="inlineStr">
+        <is>
+          <t>B | 3477呎 (4+房)
+$14008万
+$40,288/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>A | 3316呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t>B | 3477呎 (4+房)
+$17228万
+$49,549/呎
+(23年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>A | 3207呎 (4+房)
+$12106万
+$37,749/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t>B | 3627呎 (4+房)
+$13194万
+$36,379/呎
+(24年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>A | 3316呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>B | 3627呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>A | 3207呎 (4+房)
+$12066万
+$37,625/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>B | 3627呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>A | 3316呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>B | 3627呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>A | 3316呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
+        <is>
+          <t>B | 3627呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>A | 3316呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>B | 3627呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>5座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>29&amp;30</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 6866呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 3846呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 2310呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 1944呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 2310呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 1944呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 2310呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 1944呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 2310呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 1944呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 2310呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 1944呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 2310呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>B | 1824呎 (4+房)
+$7582万
+$41,566/呎
+(24年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 2310呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 1944呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 2310呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 1944呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 2310呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 1944呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 2310呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 1944呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 2310呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 1944呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 2310呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 1944呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>A | 2178呎 (4+房)
+$7339万
+$33,695/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 1944呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 2310呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 1944呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>A | 2178呎 (4+房)
+$6745万
+$30,970/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 1944呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>A | 2178呎 (4+房)
+$7251万
+$33,290/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 1944呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>A | 2178呎 (4+房)
+$6956万
+$31,937/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t>B | 1824呎 (4+房)
+$5323万
+$29,181/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>A | 2178呎 (4+房)
+$6468万
+$29,697/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t>B | 1824呎 (4+房)
+$5800万
+$31,798/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>A | 2178呎 (4+房)
+$6280万
+$28,834/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>B | 1944呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>A | 2310呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C26" s="23" t="inlineStr">
+        <is>
+          <t>B | 1824呎 (4+房)
+$5724万
+$31,379/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>A | 2310呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C27" s="23" t="inlineStr">
+        <is>
+          <t>B | 1824呎 (4+房)
+$5953万
+$32,634/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>A | 2310呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C28" s="23" t="inlineStr">
+        <is>
+          <t>B | 1824呎 (4+房)
+$5724万
+$31,379/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>A | 2310呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>B | 1944呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>6座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 3184呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 1696呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 1689呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 1696呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 1689呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 1697呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 1689呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 1697呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 1689呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 1697呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 1689呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 1697呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 1689呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 1697呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 1689呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>A | 1626呎 (4+房)
+$4910万
+$30,197/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 1689呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>A | 1626呎 (4+房)
+$4768万
+$29,323/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 1689呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>A | 1626呎 (4+房)
+$4768万
+$29,323/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 1689呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>A | 1626呎 (4+房)
+$4378万
+$26,927/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 1689呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 1697呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 1689呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>A | 1626呎 (4+房)
+$4242万
+$26,092/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>B | 1619呎 (4+房)
+$4206万
+$25,977/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>A | 1626呎 (4+房)
+$4209万
+$25,883/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>B | 1619呎 (4+房)
+$4189万
+$25,872/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>A | 1626呎 (4+房)
+$4124万
+$25,361/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>B | 1619呎 (4+房)
+$4504万
+$27,821/呎
+(24年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>A | 1626呎 (4+房)
+$4592万
+$28,239/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>B | 1619呎 (4+房)
+$4172万
+$25,768/呎
+(25年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>A | 1626呎 (4+房)
+$4158万
+$25,570/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="inlineStr">
+        <is>
+          <t>B | 1619呎 (4+房)
+$4155万
+$25,664/呎
+(24年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>A | 1626呎 (4+房)
+$4200万
+$25,830/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t>B | 1619呎 (4+房)
+$4238万
+$26,177/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>A | 1626呎 (4+房)
+$4158万
+$25,570/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t>B | 1619呎 (4+房)
+$4200万
+$25,942/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>A | 1626呎 (4+房)
+$4141万
+$25,465/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="C25" s="23" t="inlineStr">
+        <is>
+          <t>B | 1619呎 (4+房)
+$4316万
+$26,660/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>A | 1626呎 (4+房)
+$4523万
+$27,815/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C26" s="23" t="inlineStr">
+        <is>
+          <t>B | 1619呎 (4+房)
+$4150万
+$25,633/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>A | 1626呎 (4+房)
+$4163万
+$25,601/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C27" s="23" t="inlineStr">
+        <is>
+          <t>B | 1619呎 (4+房)
+$4750万
+$29,339/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>A | 1626呎 (4+房)
+$4209万
+$25,883/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C28" s="23" t="inlineStr">
+        <is>
+          <t>B | 1619呎 (4+房)
+$4273万
+$26,394/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>A | 1626呎 (4+房)
+$4327万
+$26,613/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C29" s="23" t="inlineStr">
+        <is>
+          <t>B | 1619呎 (4+房)
+$4950万
+$30,574/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>A | 1697呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>B | 1689呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>8座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>B | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>A | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>B | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>A | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>B | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>B | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>A | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>B | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>A | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>B | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>A | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>B | 1393呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>A | 1340呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>B | 1340呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/港岛-鸭脷洲-凯玥.xlsx
+++ b/files/港岛-鸭脷洲-凯玥.xlsx
@@ -667,7 +667,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-鸭脷洲-凯玥.xlsx
+++ b/files/港岛-鸭脷洲-凯玥.xlsx
@@ -657,7 +657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J297"/>
+  <dimension ref="A1:N297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -670,6 +670,10 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -727,6 +731,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -777,6 +801,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -827,6 +871,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -877,6 +941,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -927,6 +1011,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -977,6 +1081,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1027,6 +1151,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1077,6 +1221,26 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1127,6 +1291,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1177,6 +1361,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1223,6 +1427,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1269,6 +1493,26 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1315,6 +1559,26 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1365,6 +1629,26 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1411,6 +1695,26 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1457,6 +1761,26 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1507,6 +1831,26 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1553,6 +1897,26 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1599,6 +1963,26 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1645,6 +2029,26 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1691,6 +2095,26 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1737,6 +2161,26 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1783,6 +2227,26 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1829,6 +2293,26 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1875,6 +2359,26 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1921,6 +2425,26 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1967,6 +2491,26 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2013,6 +2557,26 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2059,6 +2623,26 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2105,6 +2689,26 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2151,6 +2755,26 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2197,6 +2821,26 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2243,6 +2887,26 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2289,6 +2953,26 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2335,6 +3019,26 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2381,6 +3085,26 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2427,6 +3151,26 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2473,6 +3217,26 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2519,6 +3283,26 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2565,6 +3349,26 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2611,6 +3415,26 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2657,6 +3481,26 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2703,6 +3547,26 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2749,6 +3613,26 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2795,6 +3679,26 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2845,6 +3749,26 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2895,6 +3819,26 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2945,6 +3889,26 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2995,6 +3959,26 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3045,6 +4029,26 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3095,6 +4099,26 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3145,6 +4169,26 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3195,6 +4239,26 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3245,6 +4309,26 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3295,6 +4379,26 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3345,6 +4449,26 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3395,6 +4519,26 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3445,6 +4589,26 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3495,6 +4659,26 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3541,6 +4725,26 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3587,6 +4791,26 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3633,6 +4857,26 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3683,6 +4927,26 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3729,6 +4993,26 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3775,6 +5059,26 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3821,6 +5125,26 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3871,6 +5195,26 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3917,6 +5261,26 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3963,6 +5327,26 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4009,6 +5393,26 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4055,6 +5459,26 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4101,6 +5525,26 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4147,6 +5591,26 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4193,6 +5657,26 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L75" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4243,6 +5727,26 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4289,6 +5793,26 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4339,6 +5863,26 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4385,6 +5929,26 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L79" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4431,6 +5995,26 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4477,6 +6061,26 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L81" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4523,6 +6127,26 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4569,6 +6193,26 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L83" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4615,6 +6259,26 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4661,6 +6325,26 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L85" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4711,6 +6395,26 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L86" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4757,6 +6461,26 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L87" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4807,6 +6531,26 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K88" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L88" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4853,6 +6597,26 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L89" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4899,6 +6663,26 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L90" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4945,6 +6729,26 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L91" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4991,6 +6795,26 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K92" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L92" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5041,6 +6865,26 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L93" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5091,6 +6935,26 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K94" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L94" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5141,6 +7005,26 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L95" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5191,6 +7075,26 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L96" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5241,6 +7145,26 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L97" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5291,6 +7215,26 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L98" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5341,6 +7285,26 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L99" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5391,6 +7355,26 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K100" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L100" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5441,6 +7425,26 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L101" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5491,6 +7495,26 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L102" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5537,6 +7561,26 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L103" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5587,6 +7631,26 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K104" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L104" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5637,6 +7701,26 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L105" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5687,6 +7771,26 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K106" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L106" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5737,6 +7841,26 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L107" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N107" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5787,6 +7911,26 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K108" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L108" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N108" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5837,6 +7981,26 @@
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K109" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L109" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N109" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5887,6 +8051,26 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K110" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L110" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M110" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N110" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5937,6 +8121,26 @@
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L111" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M111" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N111" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5987,6 +8191,26 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K112" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L112" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M112" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N112" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6037,6 +8261,26 @@
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K113" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L113" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6087,6 +8331,26 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K114" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L114" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M114" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N114" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6137,6 +8401,26 @@
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L115" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M115" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N115" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6187,6 +8471,26 @@
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K116" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L116" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N116" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6237,6 +8541,26 @@
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L117" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N117" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6287,6 +8611,26 @@
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K118" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L118" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N118" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6337,6 +8681,26 @@
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L119" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M119" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N119" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6387,6 +8751,26 @@
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K120" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L120" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M120" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N120" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6437,6 +8821,26 @@
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L121" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M121" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N121" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -6487,6 +8891,26 @@
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L122" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M122" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N122" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -6537,6 +8961,26 @@
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L123" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M123" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N123" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -6587,6 +9031,26 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K124" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L124" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M124" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N124" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -6633,6 +9097,26 @@
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L125" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M125" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N125" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6683,6 +9167,26 @@
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L126" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M126" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N126" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -6729,6 +9233,26 @@
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L127" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M127" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6775,6 +9299,26 @@
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K128" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L128" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M128" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N128" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6821,6 +9365,26 @@
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K129" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L129" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M129" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N129" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6871,6 +9435,26 @@
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K130" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L130" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M130" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N130" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -6917,6 +9501,26 @@
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K131" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L131" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M131" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N131" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6963,6 +9567,26 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L132" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M132" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N132" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7013,6 +9637,26 @@
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L133" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M133" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N133" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -7063,6 +9707,26 @@
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L134" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M134" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N134" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -7113,6 +9777,26 @@
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L135" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M135" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N135" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -7159,6 +9843,26 @@
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K136" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L136" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M136" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N136" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7209,6 +9913,26 @@
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K137" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L137" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M137" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N137" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -7259,6 +9983,26 @@
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K138" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L138" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M138" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N138" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -7309,6 +10053,26 @@
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K139" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L139" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M139" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N139" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -7359,6 +10123,26 @@
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K140" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L140" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M140" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N140" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -7409,6 +10193,26 @@
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K141" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L141" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M141" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N141" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7459,6 +10263,26 @@
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K142" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L142" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M142" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N142" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7509,6 +10333,26 @@
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K143" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L143" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M143" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N143" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7559,6 +10403,26 @@
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K144" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L144" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M144" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N144" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7609,6 +10473,26 @@
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K145" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L145" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M145" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N145" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7659,6 +10543,26 @@
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K146" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L146" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M146" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N146" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7709,6 +10613,26 @@
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K147" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L147" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M147" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N147" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7759,6 +10683,26 @@
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K148" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L148" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M148" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N148" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7809,6 +10753,26 @@
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K149" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L149" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M149" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N149" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7859,6 +10823,26 @@
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K150" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L150" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M150" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N150" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7909,6 +10893,26 @@
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K151" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L151" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M151" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N151" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7959,6 +10963,26 @@
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K152" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L152" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M152" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N152" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8009,6 +11033,26 @@
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K153" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L153" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M153" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N153" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8059,6 +11103,26 @@
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K154" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L154" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M154" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N154" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8105,6 +11169,26 @@
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K155" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L155" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M155" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N155" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8155,6 +11239,26 @@
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K156" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L156" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M156" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N156" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8205,6 +11309,26 @@
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K157" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L157" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M157" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N157" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8255,6 +11379,26 @@
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K158" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L158" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M158" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N158" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8305,6 +11449,26 @@
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K159" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L159" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M159" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N159" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8355,6 +11519,26 @@
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K160" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L160" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M160" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N160" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8405,6 +11589,26 @@
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K161" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L161" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M161" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N161" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8455,6 +11659,26 @@
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K162" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L162" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M162" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N162" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8505,6 +11729,26 @@
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K163" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L163" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M163" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N163" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8555,6 +11799,26 @@
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K164" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L164" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M164" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N164" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8605,6 +11869,26 @@
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K165" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L165" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M165" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N165" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8655,6 +11939,26 @@
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K166" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L166" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M166" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N166" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8705,6 +12009,26 @@
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K167" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L167" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M167" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N167" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8755,6 +12079,26 @@
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K168" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L168" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M168" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N168" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8805,6 +12149,26 @@
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L169" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M169" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N169" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8851,6 +12215,26 @@
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K170" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L170" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M170" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N170" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8901,6 +12285,26 @@
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L171" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M171" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N171" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8951,6 +12355,26 @@
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K172" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L172" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M172" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N172" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9001,6 +12425,26 @@
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L173" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M173" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N173" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9047,6 +12491,26 @@
       </c>
       <c r="J174" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K174" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L174" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M174" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N174" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9097,6 +12561,26 @@
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L175" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M175" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N175" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9143,6 +12627,26 @@
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K176" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L176" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M176" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N176" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9189,6 +12693,26 @@
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K177" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L177" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M177" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N177" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9235,6 +12759,26 @@
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K178" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L178" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M178" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N178" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9281,6 +12825,26 @@
       </c>
       <c r="J179" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K179" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L179" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M179" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N179" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9327,6 +12891,26 @@
       </c>
       <c r="J180" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K180" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L180" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M180" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N180" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9377,6 +12961,26 @@
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K181" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L181" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M181" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N181" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -9423,6 +13027,26 @@
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K182" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L182" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M182" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N182" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9469,6 +13093,26 @@
       </c>
       <c r="J183" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K183" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L183" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M183" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N183" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9519,6 +13163,26 @@
       </c>
       <c r="J184" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K184" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L184" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M184" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N184" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -9565,6 +13229,26 @@
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K185" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L185" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M185" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N185" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9615,6 +13299,26 @@
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K186" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L186" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M186" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N186" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -9661,6 +13365,26 @@
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K187" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L187" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M187" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N187" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9711,6 +13435,26 @@
       </c>
       <c r="J188" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K188" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L188" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M188" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N188" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -9761,6 +13505,26 @@
       </c>
       <c r="J189" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K189" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L189" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M189" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N189" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9811,6 +13575,26 @@
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K190" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L190" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M190" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N190" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9861,6 +13645,26 @@
       </c>
       <c r="J191" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K191" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L191" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M191" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N191" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9911,6 +13715,26 @@
       </c>
       <c r="J192" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K192" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L192" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M192" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N192" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9961,6 +13785,26 @@
       </c>
       <c r="J193" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K193" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L193" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M193" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N193" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10011,6 +13855,26 @@
       </c>
       <c r="J194" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K194" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L194" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M194" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N194" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10061,6 +13925,26 @@
       </c>
       <c r="J195" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K195" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L195" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M195" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N195" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10111,6 +13995,26 @@
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K196" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L196" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M196" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N196" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10161,6 +14065,26 @@
       </c>
       <c r="J197" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K197" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L197" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M197" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N197" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10211,6 +14135,26 @@
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K198" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L198" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M198" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N198" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10261,6 +14205,26 @@
       </c>
       <c r="J199" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K199" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L199" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M199" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N199" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10311,6 +14275,26 @@
       </c>
       <c r="J200" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K200" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L200" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M200" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N200" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10361,6 +14345,26 @@
       </c>
       <c r="J201" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K201" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L201" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M201" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N201" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10411,6 +14415,26 @@
       </c>
       <c r="J202" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K202" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L202" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M202" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N202" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10461,6 +14485,26 @@
       </c>
       <c r="J203" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K203" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L203" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M203" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N203" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10511,6 +14555,26 @@
       </c>
       <c r="J204" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K204" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L204" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M204" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N204" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10561,6 +14625,26 @@
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K205" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L205" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M205" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N205" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10611,6 +14695,26 @@
       </c>
       <c r="J206" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K206" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L206" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M206" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N206" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10657,6 +14761,26 @@
       </c>
       <c r="J207" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K207" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L207" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M207" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N207" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10707,6 +14831,26 @@
       </c>
       <c r="J208" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K208" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L208" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M208" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N208" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10753,6 +14897,26 @@
       </c>
       <c r="J209" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K209" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L209" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M209" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N209" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10803,6 +14967,26 @@
       </c>
       <c r="J210" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K210" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L210" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M210" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N210" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10849,6 +15033,26 @@
       </c>
       <c r="J211" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K211" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L211" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M211" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N211" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10899,6 +15103,26 @@
       </c>
       <c r="J212" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K212" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L212" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M212" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N212" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10945,6 +15169,26 @@
       </c>
       <c r="J213" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K213" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L213" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M213" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N213" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10995,6 +15239,26 @@
       </c>
       <c r="J214" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K214" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L214" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M214" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N214" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11045,6 +15309,26 @@
       </c>
       <c r="J215" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K215" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L215" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M215" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N215" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11091,6 +15375,26 @@
       </c>
       <c r="J216" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K216" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L216" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M216" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N216" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11137,6 +15441,26 @@
       </c>
       <c r="J217" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K217" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L217" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M217" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N217" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11183,6 +15507,26 @@
       </c>
       <c r="J218" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K218" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L218" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M218" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N218" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11229,6 +15573,26 @@
       </c>
       <c r="J219" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K219" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L219" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M219" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N219" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11275,6 +15639,26 @@
       </c>
       <c r="J220" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K220" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L220" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M220" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N220" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11321,6 +15705,26 @@
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K221" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L221" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M221" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N221" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11367,6 +15771,26 @@
       </c>
       <c r="J222" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K222" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L222" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M222" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N222" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11413,6 +15837,26 @@
       </c>
       <c r="J223" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K223" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L223" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M223" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N223" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11459,6 +15903,26 @@
       </c>
       <c r="J224" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K224" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L224" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M224" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N224" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11505,6 +15969,26 @@
       </c>
       <c r="J225" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K225" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L225" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M225" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N225" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11551,6 +16035,26 @@
       </c>
       <c r="J226" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K226" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L226" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M226" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N226" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11597,6 +16101,26 @@
       </c>
       <c r="J227" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K227" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L227" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M227" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N227" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11643,6 +16167,26 @@
       </c>
       <c r="J228" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K228" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L228" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M228" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N228" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11689,6 +16233,26 @@
       </c>
       <c r="J229" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K229" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L229" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M229" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N229" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11735,6 +16299,26 @@
       </c>
       <c r="J230" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K230" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L230" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M230" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N230" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11781,6 +16365,26 @@
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K231" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L231" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M231" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N231" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11827,6 +16431,26 @@
       </c>
       <c r="J232" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K232" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L232" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M232" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N232" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11873,6 +16497,26 @@
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K233" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L233" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M233" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N233" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11919,6 +16563,26 @@
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K234" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L234" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M234" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N234" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11965,6 +16629,26 @@
       </c>
       <c r="J235" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K235" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L235" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M235" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N235" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12011,6 +16695,26 @@
       </c>
       <c r="J236" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K236" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L236" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M236" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N236" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12057,6 +16761,26 @@
       </c>
       <c r="J237" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K237" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L237" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M237" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N237" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12103,6 +16827,26 @@
       </c>
       <c r="J238" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K238" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L238" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M238" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N238" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12149,6 +16893,26 @@
       </c>
       <c r="J239" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K239" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L239" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M239" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N239" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12199,6 +16963,26 @@
       </c>
       <c r="J240" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K240" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L240" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M240" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N240" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12249,6 +17033,26 @@
       </c>
       <c r="J241" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K241" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L241" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M241" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N241" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12299,6 +17103,26 @@
       </c>
       <c r="J242" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K242" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L242" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M242" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N242" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12349,6 +17173,26 @@
       </c>
       <c r="J243" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K243" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L243" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M243" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N243" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12399,6 +17243,26 @@
       </c>
       <c r="J244" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K244" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L244" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M244" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N244" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12449,6 +17313,26 @@
       </c>
       <c r="J245" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K245" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L245" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M245" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N245" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12499,6 +17383,26 @@
       </c>
       <c r="J246" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K246" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L246" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M246" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N246" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12549,6 +17453,26 @@
       </c>
       <c r="J247" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K247" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L247" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M247" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N247" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12599,6 +17523,26 @@
       </c>
       <c r="J248" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K248" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L248" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M248" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N248" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12649,6 +17593,26 @@
       </c>
       <c r="J249" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K249" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L249" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M249" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N249" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12699,6 +17663,26 @@
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K250" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L250" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M250" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N250" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12749,6 +17733,26 @@
       </c>
       <c r="J251" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K251" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L251" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M251" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N251" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12799,6 +17803,26 @@
       </c>
       <c r="J252" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K252" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L252" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M252" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N252" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12849,6 +17873,26 @@
       </c>
       <c r="J253" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K253" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L253" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M253" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N253" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12899,6 +17943,26 @@
       </c>
       <c r="J254" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K254" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L254" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M254" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N254" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12949,6 +18013,26 @@
       </c>
       <c r="J255" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K255" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L255" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M255" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N255" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12999,6 +18083,26 @@
       </c>
       <c r="J256" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K256" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L256" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M256" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N256" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13049,6 +18153,26 @@
       </c>
       <c r="J257" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K257" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L257" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M257" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N257" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13099,6 +18223,26 @@
       </c>
       <c r="J258" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K258" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L258" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M258" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N258" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13149,6 +18293,26 @@
       </c>
       <c r="J259" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K259" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L259" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M259" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N259" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13199,6 +18363,26 @@
       </c>
       <c r="J260" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K260" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L260" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M260" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N260" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13249,6 +18433,26 @@
       </c>
       <c r="J261" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K261" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L261" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M261" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N261" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13299,6 +18503,26 @@
       </c>
       <c r="J262" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K262" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L262" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M262" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N262" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13349,6 +18573,26 @@
       </c>
       <c r="J263" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K263" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L263" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M263" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N263" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13399,6 +18643,26 @@
       </c>
       <c r="J264" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K264" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L264" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M264" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N264" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13449,6 +18713,26 @@
       </c>
       <c r="J265" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K265" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L265" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M265" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N265" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13499,6 +18783,26 @@
       </c>
       <c r="J266" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K266" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L266" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M266" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N266" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13549,6 +18853,26 @@
       </c>
       <c r="J267" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K267" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L267" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M267" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N267" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13599,6 +18923,26 @@
       </c>
       <c r="J268" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K268" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L268" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M268" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N268" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13649,6 +18993,26 @@
       </c>
       <c r="J269" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K269" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L269" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M269" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N269" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13699,6 +19063,26 @@
       </c>
       <c r="J270" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K270" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L270" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M270" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N270" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13749,6 +19133,26 @@
       </c>
       <c r="J271" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K271" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L271" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M271" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N271" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13799,6 +19203,26 @@
       </c>
       <c r="J272" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K272" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L272" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M272" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N272" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13849,6 +19273,26 @@
       </c>
       <c r="J273" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K273" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L273" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M273" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N273" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13899,6 +19343,26 @@
       </c>
       <c r="J274" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K274" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L274" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M274" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N274" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13949,6 +19413,26 @@
       </c>
       <c r="J275" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K275" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L275" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M275" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N275" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13999,6 +19483,26 @@
       </c>
       <c r="J276" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K276" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L276" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M276" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N276" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14049,6 +19553,26 @@
       </c>
       <c r="J277" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K277" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L277" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M277" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N277" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14099,6 +19623,26 @@
       </c>
       <c r="J278" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K278" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L278" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M278" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N278" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14149,6 +19693,26 @@
       </c>
       <c r="J279" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K279" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L279" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M279" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N279" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14199,6 +19763,26 @@
       </c>
       <c r="J280" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K280" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L280" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M280" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N280" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14249,6 +19833,26 @@
       </c>
       <c r="J281" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K281" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L281" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M281" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N281" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14299,6 +19903,26 @@
       </c>
       <c r="J282" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K282" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L282" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M282" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N282" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14349,6 +19973,26 @@
       </c>
       <c r="J283" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K283" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L283" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M283" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N283" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14399,6 +20043,26 @@
       </c>
       <c r="J284" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K284" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L284" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M284" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N284" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14449,6 +20113,26 @@
       </c>
       <c r="J285" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K285" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L285" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M285" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N285" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14499,6 +20183,26 @@
       </c>
       <c r="J286" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K286" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L286" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M286" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N286" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14549,6 +20253,26 @@
       </c>
       <c r="J287" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K287" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L287" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M287" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N287" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14599,6 +20323,26 @@
       </c>
       <c r="J288" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K288" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L288" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M288" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N288" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14649,6 +20393,26 @@
       </c>
       <c r="J289" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K289" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L289" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M289" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N289" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14699,6 +20463,26 @@
       </c>
       <c r="J290" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K290" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L290" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M290" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N290" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14749,6 +20533,26 @@
       </c>
       <c r="J291" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K291" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L291" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M291" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N291" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14799,6 +20603,26 @@
       </c>
       <c r="J292" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K292" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L292" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M292" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N292" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14849,6 +20673,26 @@
       </c>
       <c r="J293" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K293" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L293" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M293" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N293" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14899,6 +20743,26 @@
       </c>
       <c r="J294" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K294" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L294" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M294" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N294" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14949,6 +20813,26 @@
       </c>
       <c r="J295" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K295" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L295" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M295" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N295" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14999,6 +20883,26 @@
       </c>
       <c r="J296" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K296" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L296" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M296" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N296" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -15049,13 +20953,33 @@
       </c>
       <c r="J297" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K297" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L297" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M297" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N297" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -15276,7 +21200,7 @@
           <t>A | 1864呎 (4+房)
 $6080万
 $32,618/呎
-(25年-09月)</t>
+(25年-09月-01日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -15299,7 +21223,7 @@
           <t>A | 1864呎 (4+房)
 $5525万
 $29,642/呎
-(25年-09月)</t>
+(25年-09月-15日)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -15307,7 +21231,7 @@
           <t>B | 2107呎 (4+房)
 $6572万
 $31,191/呎
-(25年-09月)</t>
+(25年-09月-10日)</t>
         </is>
       </c>
     </row>
@@ -15322,7 +21246,7 @@
           <t>A | 1864呎 (4+房)
 $5940万
 $31,866/呎
-(25年-07月)</t>
+(25年-07月-10日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -15353,7 +21277,7 @@
           <t>B | 2107呎 (4+房)
 $6900万
 $32,748/呎
-(24年-08月)</t>
+(24年-08月-20日)</t>
         </is>
       </c>
     </row>
@@ -15368,7 +21292,7 @@
           <t>A | 1864呎 (4+房)
 $5408万
 $29,013/呎
-(25年-07月)</t>
+(25年-07月-10日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -15376,7 +21300,7 @@
           <t>B | 2107呎 (4+房)
 $6600万
 $31,324/呎
-(24年-10月)</t>
+(24年-10月-15日)</t>
         </is>
       </c>
     </row>
@@ -15391,7 +21315,7 @@
           <t>A | 1864呎 (4+房)
 $5800万
 $31,116/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -15399,7 +21323,7 @@
           <t>B | 2107呎 (4+房)
 $6792万
 $32,234/呎
-(25年-07月)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
     </row>
@@ -15414,7 +21338,7 @@
           <t>A | 1864呎 (4+房)
 $5238万
 $28,101/呎
-(24年-10月)</t>
+(24年-10月-15日)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -15422,7 +21346,7 @@
           <t>B | 2107呎 (4+房)
 $6608万
 $31,362/呎
-(24年-09月)</t>
+(24年-09月-09日)</t>
         </is>
       </c>
     </row>
@@ -15437,7 +21361,7 @@
           <t>A | 1864呎 (4+房)
 $5183万
 $27,808/呎
-(24年-07月)</t>
+(24年-07月-16日)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -15445,7 +21369,7 @@
           <t>B | 2107呎 (4+房)
 $6446万
 $30,591/呎
-(24年-07月)</t>
+(24年-07月-11日)</t>
         </is>
       </c>
     </row>
@@ -15460,7 +21384,7 @@
           <t>A | 1864呎 (4+房)
 $5561万
 $29,835/呎
-(24年-06月)</t>
+(24年-06月-11日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -15468,7 +21392,7 @@
           <t>B | 2108呎 (4+房)
 $6189万
 $29,358/呎
-(24年-07月)</t>
+(24年-07月-03日)</t>
         </is>
       </c>
     </row>
@@ -15483,7 +21407,7 @@
           <t>A | 1864呎 (4+房)
 $5548万
 $29,765/呎
-(24年-05月)</t>
+(24年-05月-15日)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -15491,7 +21415,7 @@
           <t>B | 2108呎 (4+房)
 $6287万
 $29,825/呎
-(24年-05月)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
     </row>
@@ -15506,7 +21430,7 @@
           <t>A | 1864呎 (4+房)
 $5086万
 $27,283/呎
-(24年-05月)</t>
+(24年-05月-15日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -15514,7 +21438,7 @@
           <t>B | 2108呎 (4+房)
 $5865万
 $27,821/呎
-(24年-05月)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
     </row>
@@ -15529,7 +21453,7 @@
           <t>A | 1864呎 (4+房)
 $5526万
 $29,645/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -15537,7 +21461,7 @@
           <t>B | 2108呎 (4+房)
 $5865万
 $27,821/呎
-(24年-05月)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
     </row>
@@ -15552,7 +21476,7 @@
           <t>A | 1864呎 (4+房)
 $5546万
 $29,756/呎
-(24年-05月)</t>
+(24年-05月-15日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -15560,7 +21484,7 @@
           <t>B | 2108呎 (4+房)
 $6297万
 $29,873/呎
-(24年-05月)</t>
+(24年-05月-15日)</t>
         </is>
       </c>
     </row>
@@ -15575,7 +21499,7 @@
           <t>A | 1864呎 (4+房)
 $5546万
 $29,756/呎
-(24年-05月)</t>
+(24年-05月-15日)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -15583,7 +21507,7 @@
           <t>B | 2108呎 (4+房)
 $6297万
 $29,873/呎
-(24年-05月)</t>
+(24年-05月-15日)</t>
         </is>
       </c>
     </row>
@@ -15598,7 +21522,7 @@
           <t>A | 1864呎 (4+房)
 $5178万
 $27,778/呎
-(24年-05月)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -15606,7 +21530,7 @@
           <t>B | 2108呎 (4+房)
 $6448万
 $30,588/呎
-(24年-05月)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
     </row>
@@ -15621,7 +21545,7 @@
           <t>A | 1864呎 (4+房)
 $4920万
 $26,395/呎
-(24年-07月)</t>
+(24年-07月-11日)</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
@@ -15629,7 +21553,7 @@
           <t>B | 2108呎 (4+房)
 $6455万
 $30,619/呎
-(24年-05月)</t>
+(24年-05月-15日)</t>
         </is>
       </c>
     </row>
@@ -15644,7 +21568,7 @@
           <t>A | 1864呎 (4+房)
 $5250万
 $28,165/呎
-(25年-02月)</t>
+(25年-02月-19日)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -15652,7 +21576,7 @@
           <t>B | 2108呎 (4+房)
 $6046万
 $28,682/呎
-(24年-09月)</t>
+(24年-09月-24日)</t>
         </is>
       </c>
     </row>
@@ -15667,7 +21591,7 @@
           <t>A | 1864呎 (4+房)
 $5380万
 $28,863/呎
-(26年-01月)</t>
+(26年-01月-28日)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
@@ -15675,7 +21599,7 @@
           <t>B | 2108呎 (4+房)
 $5540万
 $26,281/呎
-(25年-01月)</t>
+(25年-01月-12日)</t>
         </is>
       </c>
     </row>
@@ -15971,7 +21895,7 @@
           <t>A | 2137呎 (4+房)
 $7094万
 $33,196/呎
-(25年-10月)</t>
+(25年-10月-22日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -15979,7 +21903,7 @@
           <t>B | 2464呎 (4+房)
 $8494万
 $34,472/呎
-(25年-10月)</t>
+(25年-10月-22日)</t>
         </is>
       </c>
     </row>
@@ -16002,7 +21926,7 @@
           <t>B | 2464呎 (4+房)
 $7994万
 $32,444/呎
-(25年-10月)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
     </row>
@@ -16017,7 +21941,7 @@
           <t>A | 2137呎 (4+房)
 $6582万
 $30,799/呎
-(25年-10月)</t>
+(25年-10月-21日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -16025,7 +21949,7 @@
           <t>B | 2464呎 (4+房)
 $8200万
 $33,279/呎
-(25年-08月)</t>
+(25年-08月-03日)</t>
         </is>
       </c>
     </row>
@@ -16048,7 +21972,7 @@
           <t>B | 2464呎 (4+房)
 $8200万
 $33,279/呎
-(25年-08月)</t>
+(25年-08月-03日)</t>
         </is>
       </c>
     </row>
@@ -16063,7 +21987,7 @@
           <t>A | 2137呎 (4+房)
 $6526万
 $30,540/呎
-(25年-04月)</t>
+(25年-04月-16日)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -16071,7 +21995,7 @@
           <t>B | 2464呎 (4+房)
 $8101万
 $32,876/呎
-(25年-04月)</t>
+(25年-04月-16日)</t>
         </is>
       </c>
     </row>
@@ -16086,7 +22010,7 @@
           <t>A | 2137呎 (4+房)
 $6526万
 $30,540/呎
-(25年-04月)</t>
+(25年-04月-16日)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -16094,7 +22018,7 @@
           <t>B | 2464呎 (4+房)
 $8101万
 $32,876/呎
-(25年-04月)</t>
+(25年-04月-16日)</t>
         </is>
       </c>
     </row>
@@ -16109,7 +22033,7 @@
           <t>A | 2137呎 (4+房)
 $6526万
 $30,540/呎
-(25年-04月)</t>
+(25年-04月-16日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -16117,7 +22041,7 @@
           <t>B | 2604呎 (4+房)
 $8101万
 $31,108/呎
-(25年-04月)</t>
+(25年-04月-16日)</t>
         </is>
       </c>
     </row>
@@ -16140,7 +22064,7 @@
           <t>B | 2464呎 (4+房)
 $8333万
 $33,818/呎
-(25年-01月)</t>
+(25年-01月-21日)</t>
         </is>
       </c>
     </row>
@@ -16163,7 +22087,7 @@
           <t>B | 2464呎 (4+房)
 $8122万
 $32,961/呎
-(25年-05月)</t>
+(25年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -16178,7 +22102,7 @@
           <t>A | 2137呎 (4+房)
 $6525万
 $30,536/呎
-(25年-02月)</t>
+(25年-02月-16日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -16186,7 +22110,7 @@
           <t>B | 2464呎 (4+房)
 $8075万
 $32,770/呎
-(25年-02月)</t>
+(25年-02月-17日)</t>
         </is>
       </c>
     </row>
@@ -16201,7 +22125,7 @@
           <t>A | 2137呎 (4+房)
 $6478万
 $30,314/呎
-(25年-09月)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -16209,7 +22133,7 @@
           <t>B | 2464呎 (4+房)
 $7900万
 $32,062/呎
-(24年-12月)</t>
+(24年-12月-03日)</t>
         </is>
       </c>
     </row>
@@ -16224,7 +22148,7 @@
           <t>A | 2137呎 (4+房)
 $7163万
 $33,520/呎
-(25年-12月)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -16232,7 +22156,7 @@
           <t>B | 2464呎 (4+房)
 $7900万
 $32,062/呎
-(24年-12月)</t>
+(24年-12月-03日)</t>
         </is>
       </c>
     </row>
@@ -16255,7 +22179,7 @@
           <t>B | 2464呎 (4+房)
 $8100万
 $32,873/呎
-(25年-06月)</t>
+(25年-06月-02日)</t>
         </is>
       </c>
     </row>
@@ -16278,7 +22202,7 @@
           <t>B | 2464呎 (4+房)
 $7853万
 $31,870/呎
-(25年-01月)</t>
+(25年-01月-14日)</t>
         </is>
       </c>
     </row>
@@ -16293,7 +22217,7 @@
           <t>A | 2137呎 (4+房)
 $7096万
 $33,206/呎
-(25年-12月)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -16301,7 +22225,7 @@
           <t>B | 2464呎 (4+房)
 $8251万
 $33,485/呎
-(25年-12月)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
     </row>
@@ -16316,7 +22240,7 @@
           <t>A | 2137呎 (4+房)
 $6723万
 $31,461/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
@@ -16324,7 +22248,7 @@
           <t>B | 2464呎 (4+房)
 $7830万
 $31,776/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
     </row>
@@ -16582,7 +22506,7 @@
           <t>B | 3635呎 (4+房)
 $18466万
 $50,800/呎
-(23年-05月)</t>
+(23年-05月-18日)</t>
         </is>
       </c>
     </row>
@@ -16835,7 +22759,7 @@
           <t>B | 3627呎 (4+房)
 $18328万
 $50,531/呎
-(23年-02月)</t>
+(23年-02月-13日)</t>
         </is>
       </c>
     </row>
@@ -16850,7 +22774,7 @@
           <t>A | 3207呎 (4+房)
 $16417万
 $51,191/呎
-(23年-01月)</t>
+(23年-01月-26日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -16858,7 +22782,7 @@
           <t>B | 3477呎 (4+房)
 $14008万
 $40,288/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
     </row>
@@ -16881,7 +22805,7 @@
           <t>B | 3477呎 (4+房)
 $17228万
 $49,549/呎
-(23年-12月)</t>
+(23年-12月-14日)</t>
         </is>
       </c>
     </row>
@@ -16896,7 +22820,7 @@
           <t>A | 3207呎 (4+房)
 $12106万
 $37,749/呎
-(24年-07月)</t>
+(24年-07月-17日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -16904,7 +22828,7 @@
           <t>B | 3627呎 (4+房)
 $13194万
 $36,379/呎
-(24年-07月)</t>
+(24年-07月-17日)</t>
         </is>
       </c>
     </row>
@@ -16942,7 +22866,7 @@
           <t>A | 3207呎 (4+房)
 $12066万
 $37,625/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
@@ -17300,7 +23224,7 @@
           <t>B | 1824呎 (4+房)
 $7582万
 $41,566/呎
-(24年-01月)</t>
+(24年-01月-21日)</t>
         </is>
       </c>
     </row>
@@ -17453,7 +23377,7 @@
           <t>A | 2178呎 (4+房)
 $7339万
 $33,695/呎
-(25年-10月)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -17499,7 +23423,7 @@
           <t>A | 2178呎 (4+房)
 $6745万
 $30,970/呎
-(25年-08月)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -17522,7 +23446,7 @@
           <t>A | 2178呎 (4+房)
 $7251万
 $33,290/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -17545,7 +23469,7 @@
           <t>A | 2178呎 (4+房)
 $6956万
 $31,937/呎
-(25年-10月)</t>
+(25年-10月-01日)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -17553,7 +23477,7 @@
           <t>B | 1824呎 (4+房)
 $5323万
 $29,181/呎
-(25年-10月)</t>
+(25年-10月-01日)</t>
         </is>
       </c>
     </row>
@@ -17568,7 +23492,7 @@
           <t>A | 2178呎 (4+房)
 $6468万
 $29,697/呎
-(24年-07月)</t>
+(24年-07月-03日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -17576,7 +23500,7 @@
           <t>B | 1824呎 (4+房)
 $5800万
 $31,798/呎
-(24年-05月)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
     </row>
@@ -17591,7 +23515,7 @@
           <t>A | 2178呎 (4+房)
 $6280万
 $28,834/呎
-(25年-07月)</t>
+(25年-07月-28日)</t>
         </is>
       </c>
       <c r="C25" s="24" t="inlineStr">
@@ -17622,7 +23546,7 @@
           <t>B | 1824呎 (4+房)
 $5724万
 $31,379/呎
-(26年-02月)</t>
+(26年-02月-01日)</t>
         </is>
       </c>
     </row>
@@ -17645,7 +23569,7 @@
           <t>B | 1824呎 (4+房)
 $5953万
 $32,634/呎
-(26年-06月)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
     </row>
@@ -17668,7 +23592,7 @@
           <t>B | 1824呎 (4+房)
 $5724万
 $31,379/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
     </row>
@@ -17994,7 +23918,7 @@
           <t>A | 1626呎 (4+房)
 $4910万
 $30,197/呎
-(25年-09月)</t>
+(25年-09月-14日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -18017,7 +23941,7 @@
           <t>A | 1626呎 (4+房)
 $4768万
 $29,323/呎
-(25年-05月)</t>
+(25年-05月-28日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -18040,7 +23964,7 @@
           <t>A | 1626呎 (4+房)
 $4768万
 $29,323/呎
-(25年-06月)</t>
+(25年-06月-01日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -18063,7 +23987,7 @@
           <t>A | 1626呎 (4+房)
 $4378万
 $26,927/呎
-(25年-06月)</t>
+(25年-06月-18日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -18109,7 +24033,7 @@
           <t>A | 1626呎 (4+房)
 $4242万
 $26,092/呎
-(25年-05月)</t>
+(25年-05月-14日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -18117,7 +24041,7 @@
           <t>B | 1619呎 (4+房)
 $4206万
 $25,977/呎
-(25年-07月)</t>
+(25年-07月-01日)</t>
         </is>
       </c>
     </row>
@@ -18132,7 +24056,7 @@
           <t>A | 1626呎 (4+房)
 $4209万
 $25,883/呎
-(25年-05月)</t>
+(25年-05月-07日)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -18140,7 +24064,7 @@
           <t>B | 1619呎 (4+房)
 $4189万
 $25,872/呎
-(25年-06月)</t>
+(25年-06月-02日)</t>
         </is>
       </c>
     </row>
@@ -18155,7 +24079,7 @@
           <t>A | 1626呎 (4+房)
 $4124万
 $25,361/呎
-(24年-06月)</t>
+(24年-06月-27日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -18163,7 +24087,7 @@
           <t>B | 1619呎 (4+房)
 $4504万
 $27,821/呎
-(24年-06月)</t>
+(24年-06月-27日)</t>
         </is>
       </c>
     </row>
@@ -18178,7 +24102,7 @@
           <t>A | 1626呎 (4+房)
 $4592万
 $28,239/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -18186,7 +24110,7 @@
           <t>B | 1619呎 (4+房)
 $4172万
 $25,768/呎
-(25年-02月)</t>
+(25年-02月-18日)</t>
         </is>
       </c>
     </row>
@@ -18201,7 +24125,7 @@
           <t>A | 1626呎 (4+房)
 $4158万
 $25,570/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -18209,7 +24133,7 @@
           <t>B | 1619呎 (4+房)
 $4155万
 $25,664/呎
-(24年-11月)</t>
+(24年-11月-10日)</t>
         </is>
       </c>
     </row>
@@ -18224,7 +24148,7 @@
           <t>A | 1626呎 (4+房)
 $4200万
 $25,830/呎
-(24年-12月)</t>
+(24年-12月-17日)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -18232,7 +24156,7 @@
           <t>B | 1619呎 (4+房)
 $4238万
 $26,177/呎
-(25年-10月)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
     </row>
@@ -18247,7 +24171,7 @@
           <t>A | 1626呎 (4+房)
 $4158万
 $25,570/呎
-(24年-11月)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -18255,7 +24179,7 @@
           <t>B | 1619呎 (4+房)
 $4200万
 $25,942/呎
-(25年-10月)</t>
+(25年-10月-05日)</t>
         </is>
       </c>
     </row>
@@ -18270,7 +24194,7 @@
           <t>A | 1626呎 (4+房)
 $4141万
 $25,465/呎
-(24年-07月)</t>
+(24年-07月-16日)</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
@@ -18278,7 +24202,7 @@
           <t>B | 1619呎 (4+房)
 $4316万
 $26,660/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
     </row>
@@ -18293,7 +24217,7 @@
           <t>A | 1626呎 (4+房)
 $4523万
 $27,815/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -18301,7 +24225,7 @@
           <t>B | 1619呎 (4+房)
 $4150万
 $25,633/呎
-(25年-10月)</t>
+(25年-10月-29日)</t>
         </is>
       </c>
     </row>
@@ -18316,7 +24240,7 @@
           <t>A | 1626呎 (4+房)
 $4163万
 $25,601/呎
-(25年-07月)</t>
+(25年-07月-01日)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
@@ -18324,7 +24248,7 @@
           <t>B | 1619呎 (4+房)
 $4750万
 $29,339/呎
-(25年-12月)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
     </row>
@@ -18339,7 +24263,7 @@
           <t>A | 1626呎 (4+房)
 $4209万
 $25,883/呎
-(25年-05月)</t>
+(25年-05月-29日)</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
@@ -18347,7 +24271,7 @@
           <t>B | 1619呎 (4+房)
 $4273万
 $26,394/呎
-(25年-12月)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
     </row>
@@ -18362,7 +24286,7 @@
           <t>A | 1626呎 (4+房)
 $4327万
 $26,613/呎
-(25年-12月)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="C29" s="23" t="inlineStr">
@@ -18370,7 +24294,7 @@
           <t>B | 1619呎 (4+房)
 $4950万
 $30,574/呎
-(26年-02月)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-鸭脷洲-凯玥.xlsx
+++ b/files/港岛-鸭脷洲-凯玥.xlsx
@@ -12941,23 +12941,19 @@
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H181" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I181" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="H181" s="5" t="n">
+        <v>63180000</v>
+      </c>
+      <c r="I181" s="5" t="n">
+        <v>32500</v>
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
@@ -12966,12 +12962,12 @@
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L181" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M181" s="3" t="inlineStr">
@@ -12981,7 +12977,7 @@
       </c>
       <c r="N181" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -23017,7 +23013,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -23027,7 +23023,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -23518,12 +23514,12 @@
 (25年-07月-28日)</t>
         </is>
       </c>
-      <c r="C25" s="24" t="inlineStr">
+      <c r="C25" s="23" t="inlineStr">
         <is>
           <t>B | 1944呎 (4+房)
-招标单位
--
-(在售)</t>
+$6318万
+$32,500/呎
+(26年-07月-14日)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-鸭脷洲-凯玥.xlsx
+++ b/files/港岛-鸭脷洲-凯玥.xlsx
@@ -12,8 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6座" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8座" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8座" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -657,7 +656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N297"/>
+  <dimension ref="A1:N246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13598,26 +13597,26 @@
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E191" s="4" t="n">
-        <v>3184</v>
+        <v>1393</v>
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
@@ -13668,26 +13667,26 @@
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E192" s="4" t="n">
-        <v>1689</v>
+        <v>1393</v>
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
@@ -13738,26 +13737,26 @@
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E193" s="4" t="n">
-        <v>1696</v>
+        <v>1393</v>
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
@@ -13808,26 +13807,26 @@
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E194" s="4" t="n">
-        <v>1689</v>
+        <v>1393</v>
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
@@ -13878,26 +13877,26 @@
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E195" s="4" t="n">
-        <v>1696</v>
+        <v>1393</v>
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
@@ -13948,26 +13947,26 @@
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E196" s="4" t="n">
-        <v>1689</v>
+        <v>1393</v>
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
@@ -14018,26 +14017,26 @@
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E197" s="4" t="n">
-        <v>1697</v>
+        <v>1393</v>
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
@@ -14088,26 +14087,26 @@
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E198" s="4" t="n">
-        <v>1689</v>
+        <v>1393</v>
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
@@ -14158,26 +14157,26 @@
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E199" s="4" t="n">
-        <v>1697</v>
+        <v>1393</v>
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
@@ -14228,30 +14227,30 @@
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E200" s="4" t="n">
-        <v>1689</v>
+        <v>1393</v>
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G200" s="3" t="inlineStr">
@@ -14298,30 +14297,30 @@
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D201" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E201" s="4" t="n">
-        <v>1697</v>
+        <v>1393</v>
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G201" s="3" t="inlineStr">
@@ -14368,30 +14367,30 @@
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D202" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E202" s="4" t="n">
-        <v>1689</v>
+        <v>1393</v>
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G202" s="3" t="inlineStr">
@@ -14438,30 +14437,30 @@
     <row r="203">
       <c r="A203" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D203" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E203" s="4" t="n">
-        <v>1697</v>
+        <v>1393</v>
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G203" s="3" t="inlineStr">
@@ -14508,30 +14507,30 @@
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E204" s="4" t="n">
-        <v>1689</v>
+        <v>1393</v>
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G204" s="3" t="inlineStr">
@@ -14578,30 +14577,30 @@
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D205" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E205" s="4" t="n">
-        <v>1697</v>
+        <v>1393</v>
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G205" s="3" t="inlineStr">
@@ -14648,30 +14647,30 @@
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D206" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E206" s="4" t="n">
-        <v>1689</v>
+        <v>1393</v>
       </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G206" s="3" t="inlineStr">
@@ -14718,42 +14717,46 @@
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D207" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E207" s="4" t="n">
-        <v>1626</v>
+        <v>1393</v>
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="H207" s="5" t="n">
-        <v>49100000</v>
-      </c>
-      <c r="I207" s="5" t="n">
-        <v>30197</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H207" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I207" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J207" s="3" t="inlineStr">
         <is>
@@ -14784,30 +14787,30 @@
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D208" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E208" s="4" t="n">
-        <v>1689</v>
+        <v>1393</v>
       </c>
       <c r="F208" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G208" s="3" t="inlineStr">
@@ -14854,42 +14857,46 @@
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D209" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E209" s="4" t="n">
-        <v>1626</v>
+        <v>1393</v>
       </c>
       <c r="F209" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="H209" s="5" t="n">
-        <v>47679924</v>
-      </c>
-      <c r="I209" s="5" t="n">
-        <v>29323</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H209" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I209" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J209" s="3" t="inlineStr">
         <is>
@@ -14920,30 +14927,30 @@
     <row r="210">
       <c r="A210" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E210" s="4" t="n">
-        <v>1689</v>
+        <v>1393</v>
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G210" s="3" t="inlineStr">
@@ -14990,42 +14997,46 @@
     <row r="211">
       <c r="A211" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D211" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E211" s="4" t="n">
-        <v>1626</v>
+        <v>1393</v>
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="H211" s="5" t="n">
-        <v>47679924</v>
-      </c>
-      <c r="I211" s="5" t="n">
-        <v>29323</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H211" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I211" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J211" s="3" t="inlineStr">
         <is>
@@ -15056,30 +15067,30 @@
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D212" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E212" s="4" t="n">
-        <v>1689</v>
+        <v>1393</v>
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G212" s="3" t="inlineStr">
@@ -15126,42 +15137,46 @@
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C213" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D213" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E213" s="4" t="n">
-        <v>1626</v>
+        <v>1393</v>
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="H213" s="5" t="n">
-        <v>43782600</v>
-      </c>
-      <c r="I213" s="5" t="n">
-        <v>26927</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H213" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I213" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J213" s="3" t="inlineStr">
         <is>
@@ -15192,30 +15207,30 @@
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D214" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E214" s="4" t="n">
-        <v>1689</v>
+        <v>1393</v>
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G214" s="3" t="inlineStr">
@@ -15262,17 +15277,17 @@
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D215" s="3" t="inlineStr">
@@ -15281,7 +15296,7 @@
         </is>
       </c>
       <c r="E215" s="4" t="n">
-        <v>1697</v>
+        <v>1393</v>
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
@@ -15332,42 +15347,46 @@
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D216" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E216" s="4" t="n">
-        <v>1619</v>
+        <v>1393</v>
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="H216" s="5" t="n">
-        <v>42056100</v>
-      </c>
-      <c r="I216" s="5" t="n">
-        <v>25977</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H216" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I216" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J216" s="3" t="inlineStr">
         <is>
@@ -15398,42 +15417,46 @@
     <row r="217">
       <c r="A217" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D217" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E217" s="4" t="n">
-        <v>1626</v>
+        <v>1393</v>
       </c>
       <c r="F217" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="H217" s="5" t="n">
-        <v>42425000</v>
-      </c>
-      <c r="I217" s="5" t="n">
-        <v>26092</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H217" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I217" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J217" s="3" t="inlineStr">
         <is>
@@ -15464,42 +15487,46 @@
     <row r="218">
       <c r="A218" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D218" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E218" s="4" t="n">
-        <v>1619</v>
+        <v>1393</v>
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="H218" s="5" t="n">
-        <v>41887200</v>
-      </c>
-      <c r="I218" s="5" t="n">
-        <v>25872</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H218" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I218" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J218" s="3" t="inlineStr">
         <is>
@@ -15530,42 +15557,46 @@
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C219" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D219" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E219" s="4" t="n">
-        <v>1626</v>
+        <v>1393</v>
       </c>
       <c r="F219" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="H219" s="5" t="n">
-        <v>42085600</v>
-      </c>
-      <c r="I219" s="5" t="n">
-        <v>25883</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H219" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I219" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J219" s="3" t="inlineStr">
         <is>
@@ -15596,42 +15627,46 @@
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D220" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E220" s="4" t="n">
-        <v>1619</v>
+        <v>1393</v>
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
-        </is>
-      </c>
-      <c r="H220" s="5" t="n">
-        <v>45042700</v>
-      </c>
-      <c r="I220" s="5" t="n">
-        <v>27821</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H220" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I220" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J220" s="3" t="inlineStr">
         <is>
@@ -15662,42 +15697,46 @@
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C221" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D221" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E221" s="4" t="n">
-        <v>1626</v>
+        <v>1393</v>
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
-        </is>
-      </c>
-      <c r="H221" s="5" t="n">
-        <v>41237100</v>
-      </c>
-      <c r="I221" s="5" t="n">
-        <v>25361</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H221" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I221" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
@@ -15728,42 +15767,46 @@
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D222" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E222" s="4" t="n">
-        <v>1619</v>
+        <v>1393</v>
       </c>
       <c r="F222" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
-        </is>
-      </c>
-      <c r="H222" s="5" t="n">
-        <v>41718300</v>
-      </c>
-      <c r="I222" s="5" t="n">
-        <v>25768</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H222" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I222" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J222" s="3" t="inlineStr">
         <is>
@@ -15794,42 +15837,46 @@
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C223" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D223" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E223" s="4" t="n">
-        <v>1626</v>
+        <v>1393</v>
       </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="H223" s="5" t="n">
-        <v>45915900</v>
-      </c>
-      <c r="I223" s="5" t="n">
-        <v>28239</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H223" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I223" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J223" s="3" t="inlineStr">
         <is>
@@ -15860,42 +15907,46 @@
     <row r="224">
       <c r="A224" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D224" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E224" s="4" t="n">
-        <v>1619</v>
+        <v>1393</v>
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="H224" s="5" t="n">
-        <v>41550000</v>
-      </c>
-      <c r="I224" s="5" t="n">
-        <v>25664</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H224" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I224" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J224" s="3" t="inlineStr">
         <is>
@@ -15926,42 +15977,46 @@
     <row r="225">
       <c r="A225" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D225" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E225" s="4" t="n">
-        <v>1626</v>
+        <v>1393</v>
       </c>
       <c r="F225" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
-        </is>
-      </c>
-      <c r="H225" s="5" t="n">
-        <v>41576500</v>
-      </c>
-      <c r="I225" s="5" t="n">
-        <v>25570</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H225" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I225" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J225" s="3" t="inlineStr">
         <is>
@@ -15992,42 +16047,46 @@
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D226" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E226" s="4" t="n">
-        <v>1619</v>
+        <v>1393</v>
       </c>
       <c r="F226" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="H226" s="5" t="n">
-        <v>42380000</v>
-      </c>
-      <c r="I226" s="5" t="n">
-        <v>26177</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H226" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I226" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J226" s="3" t="inlineStr">
         <is>
@@ -16058,42 +16117,46 @@
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C227" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D227" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E227" s="4" t="n">
-        <v>1626</v>
+        <v>1393</v>
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="H227" s="5" t="n">
-        <v>42000000</v>
-      </c>
-      <c r="I227" s="5" t="n">
-        <v>25830</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H227" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I227" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J227" s="3" t="inlineStr">
         <is>
@@ -16124,42 +16187,46 @@
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C228" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D228" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E228" s="4" t="n">
-        <v>1619</v>
+        <v>1393</v>
       </c>
       <c r="F228" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="H228" s="5" t="n">
-        <v>42000000</v>
-      </c>
-      <c r="I228" s="5" t="n">
-        <v>25942</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H228" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I228" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J228" s="3" t="inlineStr">
         <is>
@@ -16190,42 +16257,46 @@
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C229" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D229" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E229" s="4" t="n">
-        <v>1626</v>
+        <v>1393</v>
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
-        </is>
-      </c>
-      <c r="H229" s="5" t="n">
-        <v>41576500</v>
-      </c>
-      <c r="I229" s="5" t="n">
-        <v>25570</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H229" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I229" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J229" s="3" t="inlineStr">
         <is>
@@ -16256,42 +16327,46 @@
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D230" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E230" s="4" t="n">
-        <v>1619</v>
+        <v>1393</v>
       </c>
       <c r="F230" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="H230" s="5" t="n">
-        <v>43162395</v>
-      </c>
-      <c r="I230" s="5" t="n">
-        <v>26660</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H230" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I230" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J230" s="3" t="inlineStr">
         <is>
@@ -16322,42 +16397,46 @@
     <row r="231">
       <c r="A231" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C231" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D231" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E231" s="4" t="n">
-        <v>1626</v>
+        <v>1393</v>
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="H231" s="5" t="n">
-        <v>41406800</v>
-      </c>
-      <c r="I231" s="5" t="n">
-        <v>25465</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H231" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I231" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
@@ -16388,42 +16467,46 @@
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D232" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E232" s="4" t="n">
-        <v>1619</v>
+        <v>1393</v>
       </c>
       <c r="F232" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="H232" s="5" t="n">
-        <v>41500000</v>
-      </c>
-      <c r="I232" s="5" t="n">
-        <v>25633</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H232" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I232" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J232" s="3" t="inlineStr">
         <is>
@@ -16454,42 +16537,46 @@
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C233" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D233" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E233" s="4" t="n">
-        <v>1626</v>
+        <v>1393</v>
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
-        </is>
-      </c>
-      <c r="H233" s="5" t="n">
-        <v>45228000</v>
-      </c>
-      <c r="I233" s="5" t="n">
-        <v>27815</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H233" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I233" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
@@ -16520,42 +16607,46 @@
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C234" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D234" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E234" s="4" t="n">
-        <v>1619</v>
+        <v>1393</v>
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
-        </is>
-      </c>
-      <c r="H234" s="5" t="n">
-        <v>47500195</v>
-      </c>
-      <c r="I234" s="5" t="n">
-        <v>29339</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H234" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I234" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
@@ -16586,42 +16677,46 @@
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C235" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D235" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E235" s="4" t="n">
-        <v>1626</v>
+        <v>1393</v>
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="H235" s="5" t="n">
-        <v>41627410</v>
-      </c>
-      <c r="I235" s="5" t="n">
-        <v>25601</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H235" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I235" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J235" s="3" t="inlineStr">
         <is>
@@ -16652,42 +16747,46 @@
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C236" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D236" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E236" s="4" t="n">
-        <v>1619</v>
+        <v>1393</v>
       </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
-        </is>
-      </c>
-      <c r="H236" s="5" t="n">
-        <v>42731700</v>
-      </c>
-      <c r="I236" s="5" t="n">
-        <v>26394</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H236" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I236" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J236" s="3" t="inlineStr">
         <is>
@@ -16718,42 +16817,46 @@
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C237" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D237" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E237" s="4" t="n">
-        <v>1626</v>
+        <v>1393</v>
       </c>
       <c r="F237" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
-        </is>
-      </c>
-      <c r="H237" s="5" t="n">
-        <v>42085600</v>
-      </c>
-      <c r="I237" s="5" t="n">
-        <v>25883</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H237" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I237" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J237" s="3" t="inlineStr">
         <is>
@@ -16784,42 +16887,46 @@
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C238" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D238" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E238" s="4" t="n">
-        <v>1619</v>
+        <v>1393</v>
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="H238" s="5" t="n">
-        <v>49500000</v>
-      </c>
-      <c r="I238" s="5" t="n">
-        <v>30574</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H238" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I238" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J238" s="3" t="inlineStr">
         <is>
@@ -16850,42 +16957,46 @@
     <row r="239">
       <c r="A239" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D239" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E239" s="4" t="n">
-        <v>1626</v>
+        <v>1393</v>
       </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
-        </is>
-      </c>
-      <c r="H239" s="5" t="n">
-        <v>43273500</v>
-      </c>
-      <c r="I239" s="5" t="n">
-        <v>26613</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H239" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I239" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J239" s="3" t="inlineStr">
         <is>
@@ -16916,26 +17027,26 @@
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D240" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E240" s="4" t="n">
-        <v>1689</v>
+        <v>1393</v>
       </c>
       <c r="F240" s="3" t="inlineStr">
         <is>
@@ -16986,26 +17097,26 @@
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D241" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E241" s="4" t="n">
-        <v>1697</v>
+        <v>1393</v>
       </c>
       <c r="F241" s="3" t="inlineStr">
         <is>
@@ -17061,12 +17172,12 @@
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D242" s="3" t="inlineStr">
@@ -17131,12 +17242,12 @@
       </c>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D243" s="3" t="inlineStr">
@@ -17201,12 +17312,12 @@
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C244" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D244" s="3" t="inlineStr">
@@ -17271,12 +17382,12 @@
       </c>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C245" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D245" s="3" t="inlineStr">
@@ -17285,7 +17396,7 @@
         </is>
       </c>
       <c r="E245" s="4" t="n">
-        <v>1393</v>
+        <v>1340</v>
       </c>
       <c r="F245" s="3" t="inlineStr">
         <is>
@@ -17341,12 +17452,12 @@
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C246" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D246" s="3" t="inlineStr">
@@ -17355,7 +17466,7 @@
         </is>
       </c>
       <c r="E246" s="4" t="n">
-        <v>1393</v>
+        <v>1340</v>
       </c>
       <c r="F246" s="3" t="inlineStr">
         <is>
@@ -17398,3576 +17509,6 @@
         </is>
       </c>
       <c r="N246" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B247" s="3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="C247" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D247" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E247" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="F247" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G247" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H247" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I247" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J247" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K247" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L247" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M247" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N247" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B248" s="3" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="C248" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D248" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E248" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="F248" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G248" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H248" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I248" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J248" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K248" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L248" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M248" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N248" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B249" s="3" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="C249" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D249" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E249" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="F249" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G249" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H249" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I249" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J249" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K249" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L249" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M249" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N249" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B250" s="3" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="C250" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D250" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E250" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="F250" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G250" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H250" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I250" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J250" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K250" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L250" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M250" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N250" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B251" s="3" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="C251" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D251" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E251" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="F251" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G251" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H251" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I251" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J251" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K251" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L251" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M251" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N251" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B252" s="3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="C252" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D252" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E252" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="F252" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G252" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H252" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I252" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J252" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K252" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L252" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M252" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N252" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B253" s="3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="C253" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D253" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E253" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="F253" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G253" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H253" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I253" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J253" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K253" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L253" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M253" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N253" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B254" s="3" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="C254" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D254" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E254" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="F254" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G254" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H254" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I254" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J254" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K254" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L254" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M254" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N254" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B255" s="3" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="C255" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D255" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E255" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="F255" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G255" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H255" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I255" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J255" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K255" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L255" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M255" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N255" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B256" s="3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="C256" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D256" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E256" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="F256" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G256" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H256" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I256" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J256" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K256" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L256" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M256" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N256" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B257" s="3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="C257" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D257" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E257" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="F257" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G257" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H257" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I257" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J257" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K257" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L257" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M257" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N257" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B258" s="3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="C258" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D258" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E258" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="F258" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G258" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H258" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I258" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J258" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K258" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L258" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M258" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N258" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B259" s="3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="C259" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D259" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E259" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="F259" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G259" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H259" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I259" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J259" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K259" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L259" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M259" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N259" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B260" s="3" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="C260" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D260" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E260" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="F260" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G260" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H260" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I260" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J260" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K260" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L260" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M260" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N260" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B261" s="3" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="C261" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D261" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E261" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="F261" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G261" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H261" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I261" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J261" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K261" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L261" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M261" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N261" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B262" s="3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="C262" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D262" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E262" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="F262" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G262" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H262" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I262" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J262" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K262" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L262" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M262" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N262" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B263" s="3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="C263" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D263" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E263" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="F263" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G263" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H263" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I263" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J263" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K263" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L263" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M263" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N263" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B264" s="3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="C264" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D264" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E264" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="F264" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G264" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H264" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I264" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J264" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K264" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L264" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M264" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N264" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B265" s="3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="C265" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D265" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E265" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="F265" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G265" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H265" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I265" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J265" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K265" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L265" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M265" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N265" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B266" s="3" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="C266" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D266" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E266" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="F266" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G266" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H266" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I266" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J266" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K266" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L266" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M266" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N266" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B267" s="3" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="C267" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D267" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E267" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="F267" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G267" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H267" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I267" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J267" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K267" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L267" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M267" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N267" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B268" s="3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="C268" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D268" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E268" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="F268" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G268" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H268" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I268" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J268" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K268" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L268" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M268" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N268" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B269" s="3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="C269" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D269" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E269" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="F269" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G269" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H269" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I269" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J269" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K269" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L269" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M269" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N269" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B270" s="3" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="C270" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D270" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E270" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="F270" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G270" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H270" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I270" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J270" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K270" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L270" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M270" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N270" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B271" s="3" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="C271" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D271" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E271" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="F271" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G271" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H271" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I271" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J271" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K271" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L271" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M271" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N271" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B272" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C272" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D272" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E272" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="F272" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G272" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H272" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I272" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J272" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K272" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L272" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M272" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N272" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B273" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C273" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D273" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E273" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="F273" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G273" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H273" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I273" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J273" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K273" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L273" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M273" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N273" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B274" s="3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="C274" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D274" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E274" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="F274" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G274" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H274" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I274" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J274" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K274" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L274" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M274" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N274" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B275" s="3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="C275" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D275" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E275" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="F275" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G275" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H275" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I275" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J275" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K275" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L275" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M275" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N275" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B276" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C276" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D276" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E276" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="F276" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G276" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H276" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I276" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J276" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K276" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L276" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M276" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N276" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B277" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C277" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D277" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E277" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="F277" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G277" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H277" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I277" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J277" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K277" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L277" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M277" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N277" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B278" s="3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C278" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D278" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E278" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="F278" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G278" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H278" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I278" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J278" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K278" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L278" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M278" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N278" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B279" s="3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C279" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D279" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E279" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="F279" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G279" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H279" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I279" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J279" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K279" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L279" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M279" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N279" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B280" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C280" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D280" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E280" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="F280" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G280" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H280" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I280" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J280" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K280" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L280" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M280" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N280" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B281" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C281" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D281" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E281" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="F281" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G281" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H281" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I281" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J281" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K281" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L281" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M281" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N281" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B282" s="3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C282" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D282" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E282" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="F282" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G282" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H282" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I282" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J282" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K282" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L282" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M282" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N282" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B283" s="3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C283" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D283" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E283" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="F283" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G283" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H283" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I283" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J283" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K283" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L283" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M283" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N283" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B284" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C284" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D284" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E284" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="F284" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G284" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H284" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I284" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J284" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K284" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L284" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M284" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N284" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B285" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C285" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D285" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E285" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="F285" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G285" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H285" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I285" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J285" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K285" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L285" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M285" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N285" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B286" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C286" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D286" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E286" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="F286" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G286" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H286" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I286" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J286" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K286" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L286" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M286" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N286" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B287" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C287" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D287" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E287" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="F287" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G287" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H287" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I287" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J287" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K287" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L287" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M287" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N287" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B288" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C288" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D288" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E288" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="F288" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G288" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H288" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I288" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J288" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K288" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L288" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M288" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N288" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B289" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C289" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D289" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E289" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="F289" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G289" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H289" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I289" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J289" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K289" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L289" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M289" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N289" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B290" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C290" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D290" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E290" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="F290" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G290" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H290" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I290" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J290" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K290" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L290" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M290" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N290" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B291" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C291" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D291" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E291" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="F291" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G291" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H291" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I291" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J291" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K291" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L291" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M291" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N291" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B292" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C292" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D292" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E292" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="F292" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G292" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H292" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I292" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J292" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K292" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L292" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M292" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N292" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B293" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C293" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D293" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E293" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="F293" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G293" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H293" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I293" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J293" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K293" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L293" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M293" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N293" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B294" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C294" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D294" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E294" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="F294" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G294" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H294" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I294" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J294" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K294" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L294" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M294" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N294" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B295" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C295" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D295" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E295" s="4" t="n">
-        <v>1393</v>
-      </c>
-      <c r="F295" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G295" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H295" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I295" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J295" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K295" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L295" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M295" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N295" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B296" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C296" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D296" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E296" s="4" t="n">
-        <v>1340</v>
-      </c>
-      <c r="F296" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G296" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H296" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I296" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J296" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K296" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L296" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M296" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N296" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" s="3" t="inlineStr">
-        <is>
-          <t>8座</t>
-        </is>
-      </c>
-      <c r="B297" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C297" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D297" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E297" s="4" t="n">
-        <v>1340</v>
-      </c>
-      <c r="F297" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G297" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H297" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I297" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J297" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K297" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L297" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M297" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N297" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -21196,7 +17737,7 @@
           <t>A | 1864呎 (4+房)
 $6080万
 $32,618/呎
-(25年-09月-01日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -21219,7 +17760,7 @@
           <t>A | 1864呎 (4+房)
 $5525万
 $29,642/呎
-(25年-09月-15日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -21227,7 +17768,7 @@
           <t>B | 2107呎 (4+房)
 $6572万
 $31,191/呎
-(25年-09月-10日)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -21242,7 +17783,7 @@
           <t>A | 1864呎 (4+房)
 $5940万
 $31,866/呎
-(25年-07月-10日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -21273,7 +17814,7 @@
           <t>B | 2107呎 (4+房)
 $6900万
 $32,748/呎
-(24年-08月-20日)</t>
+(24年-08月)</t>
         </is>
       </c>
     </row>
@@ -21288,7 +17829,7 @@
           <t>A | 1864呎 (4+房)
 $5408万
 $29,013/呎
-(25年-07月-10日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -21296,7 +17837,7 @@
           <t>B | 2107呎 (4+房)
 $6600万
 $31,324/呎
-(24年-10月-15日)</t>
+(24年-10月)</t>
         </is>
       </c>
     </row>
@@ -21311,7 +17852,7 @@
           <t>A | 1864呎 (4+房)
 $5800万
 $31,116/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -21319,7 +17860,7 @@
           <t>B | 2107呎 (4+房)
 $6792万
 $32,234/呎
-(25年-07月-14日)</t>
+(25年-07月)</t>
         </is>
       </c>
     </row>
@@ -21334,7 +17875,7 @@
           <t>A | 1864呎 (4+房)
 $5238万
 $28,101/呎
-(24年-10月-15日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -21342,7 +17883,7 @@
           <t>B | 2107呎 (4+房)
 $6608万
 $31,362/呎
-(24年-09月-09日)</t>
+(24年-09月)</t>
         </is>
       </c>
     </row>
@@ -21357,7 +17898,7 @@
           <t>A | 1864呎 (4+房)
 $5183万
 $27,808/呎
-(24年-07月-16日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -21365,7 +17906,7 @@
           <t>B | 2107呎 (4+房)
 $6446万
 $30,591/呎
-(24年-07月-11日)</t>
+(24年-07月)</t>
         </is>
       </c>
     </row>
@@ -21380,7 +17921,7 @@
           <t>A | 1864呎 (4+房)
 $5561万
 $29,835/呎
-(24年-06月-11日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -21388,7 +17929,7 @@
           <t>B | 2108呎 (4+房)
 $6189万
 $29,358/呎
-(24年-07月-03日)</t>
+(24年-07月)</t>
         </is>
       </c>
     </row>
@@ -21403,7 +17944,7 @@
           <t>A | 1864呎 (4+房)
 $5548万
 $29,765/呎
-(24年-05月-15日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -21411,7 +17952,7 @@
           <t>B | 2108呎 (4+房)
 $6287万
 $29,825/呎
-(24年-05月-16日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -21426,7 +17967,7 @@
           <t>A | 1864呎 (4+房)
 $5086万
 $27,283/呎
-(24年-05月-15日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -21434,7 +17975,7 @@
           <t>B | 2108呎 (4+房)
 $5865万
 $27,821/呎
-(24年-05月-16日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -21449,7 +17990,7 @@
           <t>A | 1864呎 (4+房)
 $5526万
 $29,645/呎
-(24年-05月-20日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -21457,7 +17998,7 @@
           <t>B | 2108呎 (4+房)
 $5865万
 $27,821/呎
-(24年-05月-16日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -21472,7 +18013,7 @@
           <t>A | 1864呎 (4+房)
 $5546万
 $29,756/呎
-(24年-05月-15日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -21480,7 +18021,7 @@
           <t>B | 2108呎 (4+房)
 $6297万
 $29,873/呎
-(24年-05月-15日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -21495,7 +18036,7 @@
           <t>A | 1864呎 (4+房)
 $5546万
 $29,756/呎
-(24年-05月-15日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -21503,7 +18044,7 @@
           <t>B | 2108呎 (4+房)
 $6297万
 $29,873/呎
-(24年-05月-15日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -21518,7 +18059,7 @@
           <t>A | 1864呎 (4+房)
 $5178万
 $27,778/呎
-(24年-05月-16日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -21526,7 +18067,7 @@
           <t>B | 2108呎 (4+房)
 $6448万
 $30,588/呎
-(24年-05月-16日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -21541,7 +18082,7 @@
           <t>A | 1864呎 (4+房)
 $4920万
 $26,395/呎
-(24年-07月-11日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
@@ -21549,7 +18090,7 @@
           <t>B | 2108呎 (4+房)
 $6455万
 $30,619/呎
-(24年-05月-15日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -21564,7 +18105,7 @@
           <t>A | 1864呎 (4+房)
 $5250万
 $28,165/呎
-(25年-02月-19日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -21572,7 +18113,7 @@
           <t>B | 2108呎 (4+房)
 $6046万
 $28,682/呎
-(24年-09月-24日)</t>
+(24年-09月)</t>
         </is>
       </c>
     </row>
@@ -21587,7 +18128,7 @@
           <t>A | 1864呎 (4+房)
 $5380万
 $28,863/呎
-(26年-01月-28日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
@@ -21595,7 +18136,7 @@
           <t>B | 2108呎 (4+房)
 $5540万
 $26,281/呎
-(25年-01月-12日)</t>
+(25年-01月)</t>
         </is>
       </c>
     </row>
@@ -21891,7 +18432,7 @@
           <t>A | 2137呎 (4+房)
 $7094万
 $33,196/呎
-(25年-10月-22日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -21899,7 +18440,7 @@
           <t>B | 2464呎 (4+房)
 $8494万
 $34,472/呎
-(25年-10月-22日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -21922,7 +18463,7 @@
           <t>B | 2464呎 (4+房)
 $7994万
 $32,444/呎
-(25年-10月-15日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -21937,7 +18478,7 @@
           <t>A | 2137呎 (4+房)
 $6582万
 $30,799/呎
-(25年-10月-21日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -21945,7 +18486,7 @@
           <t>B | 2464呎 (4+房)
 $8200万
 $33,279/呎
-(25年-08月-03日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -21968,7 +18509,7 @@
           <t>B | 2464呎 (4+房)
 $8200万
 $33,279/呎
-(25年-08月-03日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -21983,7 +18524,7 @@
           <t>A | 2137呎 (4+房)
 $6526万
 $30,540/呎
-(25年-04月-16日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -21991,7 +18532,7 @@
           <t>B | 2464呎 (4+房)
 $8101万
 $32,876/呎
-(25年-04月-16日)</t>
+(25年-04月)</t>
         </is>
       </c>
     </row>
@@ -22006,7 +18547,7 @@
           <t>A | 2137呎 (4+房)
 $6526万
 $30,540/呎
-(25年-04月-16日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -22014,7 +18555,7 @@
           <t>B | 2464呎 (4+房)
 $8101万
 $32,876/呎
-(25年-04月-16日)</t>
+(25年-04月)</t>
         </is>
       </c>
     </row>
@@ -22029,7 +18570,7 @@
           <t>A | 2137呎 (4+房)
 $6526万
 $30,540/呎
-(25年-04月-16日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -22037,7 +18578,7 @@
           <t>B | 2604呎 (4+房)
 $8101万
 $31,108/呎
-(25年-04月-16日)</t>
+(25年-04月)</t>
         </is>
       </c>
     </row>
@@ -22060,7 +18601,7 @@
           <t>B | 2464呎 (4+房)
 $8333万
 $33,818/呎
-(25年-01月-21日)</t>
+(25年-01月)</t>
         </is>
       </c>
     </row>
@@ -22083,7 +18624,7 @@
           <t>B | 2464呎 (4+房)
 $8122万
 $32,961/呎
-(25年-05月-22日)</t>
+(25年-05月)</t>
         </is>
       </c>
     </row>
@@ -22098,7 +18639,7 @@
           <t>A | 2137呎 (4+房)
 $6525万
 $30,536/呎
-(25年-02月-16日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -22106,7 +18647,7 @@
           <t>B | 2464呎 (4+房)
 $8075万
 $32,770/呎
-(25年-02月-17日)</t>
+(25年-02月)</t>
         </is>
       </c>
     </row>
@@ -22121,7 +18662,7 @@
           <t>A | 2137呎 (4+房)
 $6478万
 $30,314/呎
-(25年-09月-29日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -22129,7 +18670,7 @@
           <t>B | 2464呎 (4+房)
 $7900万
 $32,062/呎
-(24年-12月-03日)</t>
+(24年-12月)</t>
         </is>
       </c>
     </row>
@@ -22144,7 +18685,7 @@
           <t>A | 2137呎 (4+房)
 $7163万
 $33,520/呎
-(25年-12月-18日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -22152,7 +18693,7 @@
           <t>B | 2464呎 (4+房)
 $7900万
 $32,062/呎
-(24年-12月-03日)</t>
+(24年-12月)</t>
         </is>
       </c>
     </row>
@@ -22175,7 +18716,7 @@
           <t>B | 2464呎 (4+房)
 $8100万
 $32,873/呎
-(25年-06月-02日)</t>
+(25年-06月)</t>
         </is>
       </c>
     </row>
@@ -22198,7 +18739,7 @@
           <t>B | 2464呎 (4+房)
 $7853万
 $31,870/呎
-(25年-01月-14日)</t>
+(25年-01月)</t>
         </is>
       </c>
     </row>
@@ -22213,7 +18754,7 @@
           <t>A | 2137呎 (4+房)
 $7096万
 $33,206/呎
-(25年-12月-18日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -22221,7 +18762,7 @@
           <t>B | 2464呎 (4+房)
 $8251万
 $33,485/呎
-(25年-12月-18日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -22236,7 +18777,7 @@
           <t>A | 2137呎 (4+房)
 $6723万
 $31,461/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
@@ -22244,7 +18785,7 @@
           <t>B | 2464呎 (4+房)
 $7830万
 $31,776/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -22502,7 +19043,7 @@
           <t>B | 3635呎 (4+房)
 $18466万
 $50,800/呎
-(23年-05月-18日)</t>
+(23年-05月)</t>
         </is>
       </c>
     </row>
@@ -22755,7 +19296,7 @@
           <t>B | 3627呎 (4+房)
 $18328万
 $50,531/呎
-(23年-02月-13日)</t>
+(23年-02月)</t>
         </is>
       </c>
     </row>
@@ -22770,7 +19311,7 @@
           <t>A | 3207呎 (4+房)
 $16417万
 $51,191/呎
-(23年-01月-26日)</t>
+(23年-01月)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -22778,7 +19319,7 @@
           <t>B | 3477呎 (4+房)
 $14008万
 $40,288/呎
-(26年-05月-03日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -22801,7 +19342,7 @@
           <t>B | 3477呎 (4+房)
 $17228万
 $49,549/呎
-(23年-12月-14日)</t>
+(23年-12月)</t>
         </is>
       </c>
     </row>
@@ -22816,7 +19357,7 @@
           <t>A | 3207呎 (4+房)
 $12106万
 $37,749/呎
-(24年-07月-17日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -22824,7 +19365,7 @@
           <t>B | 3627呎 (4+房)
 $13194万
 $36,379/呎
-(24年-07月-17日)</t>
+(24年-07月)</t>
         </is>
       </c>
     </row>
@@ -22862,7 +19403,7 @@
           <t>A | 3207呎 (4+房)
 $12066万
 $37,625/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
@@ -23220,7 +19761,7 @@
           <t>B | 1824呎 (4+房)
 $7582万
 $41,566/呎
-(24年-01月-21日)</t>
+(24年-01月)</t>
         </is>
       </c>
     </row>
@@ -23373,7 +19914,7 @@
           <t>A | 2178呎 (4+房)
 $7339万
 $33,695/呎
-(25年-10月-08日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -23419,7 +19960,7 @@
           <t>A | 2178呎 (4+房)
 $6745万
 $30,970/呎
-(25年-08月-11日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -23442,7 +19983,7 @@
           <t>A | 2178呎 (4+房)
 $7251万
 $33,290/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -23465,7 +20006,7 @@
           <t>A | 2178呎 (4+房)
 $6956万
 $31,937/呎
-(25年-10月-01日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -23473,7 +20014,7 @@
           <t>B | 1824呎 (4+房)
 $5323万
 $29,181/呎
-(25年-10月-01日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -23488,7 +20029,7 @@
           <t>A | 2178呎 (4+房)
 $6468万
 $29,697/呎
-(24年-07月-03日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -23496,7 +20037,7 @@
           <t>B | 1824呎 (4+房)
 $5800万
 $31,798/呎
-(24年-05月-16日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -23511,7 +20052,7 @@
           <t>A | 2178呎 (4+房)
 $6280万
 $28,834/呎
-(25年-07月-28日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
@@ -23519,7 +20060,7 @@
           <t>B | 1944呎 (4+房)
 $6318万
 $32,500/呎
-(26年-07月-14日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -23542,7 +20083,7 @@
           <t>B | 1824呎 (4+房)
 $5724万
 $31,379/呎
-(26年-02月-01日)</t>
+(26年-02月)</t>
         </is>
       </c>
     </row>
@@ -23565,7 +20106,7 @@
           <t>B | 1824呎 (4+房)
 $5953万
 $32,634/呎
-(26年-06月-23日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -23588,7 +20129,7 @@
           <t>B | 1824呎 (4+房)
 $5724万
 $31,379/呎
-(26年-03月-02日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -23630,708 +20171,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>6座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="9" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="10" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="11" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="12" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="B3" s="14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="19" t="inlineStr">
-        <is>
-          <t>楼层</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C4" s="19" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="inlineStr">
-        <is>
-          <t>A | 3184呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C5" s="21" t="inlineStr"/>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 1696呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>B | 1689呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 1696呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>B | 1689呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B8" s="20" t="inlineStr">
-        <is>
-          <t>A | 1697呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="inlineStr">
-        <is>
-          <t>B | 1689呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="inlineStr">
-        <is>
-          <t>A | 1697呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="20" t="inlineStr">
-        <is>
-          <t>B | 1689呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B10" s="22" t="inlineStr">
-        <is>
-          <t>A | 1697呎 (4+房)
--
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C10" s="22" t="inlineStr">
-        <is>
-          <t>B | 1689呎 (4+房)
--
--
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B11" s="22" t="inlineStr">
-        <is>
-          <t>A | 1697呎 (4+房)
--
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C11" s="22" t="inlineStr">
-        <is>
-          <t>B | 1689呎 (4+房)
--
--
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B12" s="22" t="inlineStr">
-        <is>
-          <t>A | 1697呎 (4+房)
--
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C12" s="22" t="inlineStr">
-        <is>
-          <t>B | 1689呎 (4+房)
--
--
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B13" s="23" t="inlineStr">
-        <is>
-          <t>A | 1626呎 (4+房)
-$4910万
-$30,197/呎
-(25年-09月-14日)</t>
-        </is>
-      </c>
-      <c r="C13" s="22" t="inlineStr">
-        <is>
-          <t>B | 1689呎 (4+房)
--
--
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B14" s="23" t="inlineStr">
-        <is>
-          <t>A | 1626呎 (4+房)
-$4768万
-$29,323/呎
-(25年-05月-28日)</t>
-        </is>
-      </c>
-      <c r="C14" s="22" t="inlineStr">
-        <is>
-          <t>B | 1689呎 (4+房)
--
--
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B15" s="23" t="inlineStr">
-        <is>
-          <t>A | 1626呎 (4+房)
-$4768万
-$29,323/呎
-(25年-06月-01日)</t>
-        </is>
-      </c>
-      <c r="C15" s="22" t="inlineStr">
-        <is>
-          <t>B | 1689呎 (4+房)
--
--
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B16" s="23" t="inlineStr">
-        <is>
-          <t>A | 1626呎 (4+房)
-$4378万
-$26,927/呎
-(25年-06月-18日)</t>
-        </is>
-      </c>
-      <c r="C16" s="22" t="inlineStr">
-        <is>
-          <t>B | 1689呎 (4+房)
--
--
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B17" s="20" t="inlineStr">
-        <is>
-          <t>A | 1697呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="22" t="inlineStr">
-        <is>
-          <t>B | 1689呎 (4+房)
--
--
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B18" s="23" t="inlineStr">
-        <is>
-          <t>A | 1626呎 (4+房)
-$4242万
-$26,092/呎
-(25年-05月-14日)</t>
-        </is>
-      </c>
-      <c r="C18" s="23" t="inlineStr">
-        <is>
-          <t>B | 1619呎 (4+房)
-$4206万
-$25,977/呎
-(25年-07月-01日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B19" s="23" t="inlineStr">
-        <is>
-          <t>A | 1626呎 (4+房)
-$4209万
-$25,883/呎
-(25年-05月-07日)</t>
-        </is>
-      </c>
-      <c r="C19" s="23" t="inlineStr">
-        <is>
-          <t>B | 1619呎 (4+房)
-$4189万
-$25,872/呎
-(25年-06月-02日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B20" s="23" t="inlineStr">
-        <is>
-          <t>A | 1626呎 (4+房)
-$4124万
-$25,361/呎
-(24年-06月-27日)</t>
-        </is>
-      </c>
-      <c r="C20" s="23" t="inlineStr">
-        <is>
-          <t>B | 1619呎 (4+房)
-$4504万
-$27,821/呎
-(24年-06月-27日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B21" s="23" t="inlineStr">
-        <is>
-          <t>A | 1626呎 (4+房)
-$4592万
-$28,239/呎
-(24年-11月-06日)</t>
-        </is>
-      </c>
-      <c r="C21" s="23" t="inlineStr">
-        <is>
-          <t>B | 1619呎 (4+房)
-$4172万
-$25,768/呎
-(25年-02月-18日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B22" s="23" t="inlineStr">
-        <is>
-          <t>A | 1626呎 (4+房)
-$4158万
-$25,570/呎
-(24年-10月-30日)</t>
-        </is>
-      </c>
-      <c r="C22" s="23" t="inlineStr">
-        <is>
-          <t>B | 1619呎 (4+房)
-$4155万
-$25,664/呎
-(24年-11月-10日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B23" s="23" t="inlineStr">
-        <is>
-          <t>A | 1626呎 (4+房)
-$4200万
-$25,830/呎
-(24年-12月-17日)</t>
-        </is>
-      </c>
-      <c r="C23" s="23" t="inlineStr">
-        <is>
-          <t>B | 1619呎 (4+房)
-$4238万
-$26,177/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B24" s="23" t="inlineStr">
-        <is>
-          <t>A | 1626呎 (4+房)
-$4158万
-$25,570/呎
-(24年-11月-21日)</t>
-        </is>
-      </c>
-      <c r="C24" s="23" t="inlineStr">
-        <is>
-          <t>B | 1619呎 (4+房)
-$4200万
-$25,942/呎
-(25年-10月-05日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B25" s="23" t="inlineStr">
-        <is>
-          <t>A | 1626呎 (4+房)
-$4141万
-$25,465/呎
-(24年-07月-16日)</t>
-        </is>
-      </c>
-      <c r="C25" s="23" t="inlineStr">
-        <is>
-          <t>B | 1619呎 (4+房)
-$4316万
-$26,660/呎
-(25年-12月-03日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="58" customHeight="1">
-      <c r="A26" s="19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B26" s="23" t="inlineStr">
-        <is>
-          <t>A | 1626呎 (4+房)
-$4523万
-$27,815/呎
-(24年-10月-30日)</t>
-        </is>
-      </c>
-      <c r="C26" s="23" t="inlineStr">
-        <is>
-          <t>B | 1619呎 (4+房)
-$4150万
-$25,633/呎
-(25年-10月-29日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="58" customHeight="1">
-      <c r="A27" s="19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B27" s="23" t="inlineStr">
-        <is>
-          <t>A | 1626呎 (4+房)
-$4163万
-$25,601/呎
-(25年-07月-01日)</t>
-        </is>
-      </c>
-      <c r="C27" s="23" t="inlineStr">
-        <is>
-          <t>B | 1619呎 (4+房)
-$4750万
-$29,339/呎
-(25年-12月-10日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="58" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B28" s="23" t="inlineStr">
-        <is>
-          <t>A | 1626呎 (4+房)
-$4209万
-$25,883/呎
-(25年-05月-29日)</t>
-        </is>
-      </c>
-      <c r="C28" s="23" t="inlineStr">
-        <is>
-          <t>B | 1619呎 (4+房)
-$4273万
-$26,394/呎
-(25年-12月-17日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="58" customHeight="1">
-      <c r="A29" s="19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B29" s="23" t="inlineStr">
-        <is>
-          <t>A | 1626呎 (4+房)
-$4327万
-$26,613/呎
-(25年-12月-10日)</t>
-        </is>
-      </c>
-      <c r="C29" s="23" t="inlineStr">
-        <is>
-          <t>B | 1619呎 (4+房)
-$4950万
-$30,574/呎
-(26年-02月-09日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="58" customHeight="1">
-      <c r="A30" s="19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B30" s="20" t="inlineStr">
-        <is>
-          <t>A | 1697呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C30" s="20" t="inlineStr">
-        <is>
-          <t>B | 1689呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
   <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/files/港岛-鸭脷洲-凯玥.xlsx
+++ b/files/港岛-鸭脷洲-凯玥.xlsx
@@ -12,7 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8座" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6座" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8座" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -656,7 +657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N246"/>
+  <dimension ref="A1:N297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13597,26 +13598,26 @@
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E191" s="4" t="n">
-        <v>1393</v>
+        <v>3184</v>
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
@@ -13667,26 +13668,26 @@
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E192" s="4" t="n">
-        <v>1393</v>
+        <v>1689</v>
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
@@ -13737,26 +13738,26 @@
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E193" s="4" t="n">
-        <v>1393</v>
+        <v>1696</v>
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
@@ -13807,26 +13808,26 @@
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E194" s="4" t="n">
-        <v>1393</v>
+        <v>1689</v>
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
@@ -13877,26 +13878,26 @@
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E195" s="4" t="n">
-        <v>1393</v>
+        <v>1696</v>
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
@@ -13947,26 +13948,26 @@
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E196" s="4" t="n">
-        <v>1393</v>
+        <v>1689</v>
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
@@ -14017,26 +14018,26 @@
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E197" s="4" t="n">
-        <v>1393</v>
+        <v>1697</v>
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
@@ -14087,26 +14088,26 @@
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E198" s="4" t="n">
-        <v>1393</v>
+        <v>1689</v>
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
@@ -14157,26 +14158,26 @@
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E199" s="4" t="n">
-        <v>1393</v>
+        <v>1697</v>
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
@@ -14227,30 +14228,30 @@
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E200" s="4" t="n">
-        <v>1393</v>
+        <v>1689</v>
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G200" s="3" t="inlineStr">
@@ -14297,30 +14298,30 @@
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D201" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E201" s="4" t="n">
-        <v>1393</v>
+        <v>1697</v>
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G201" s="3" t="inlineStr">
@@ -14367,30 +14368,30 @@
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D202" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E202" s="4" t="n">
-        <v>1393</v>
+        <v>1689</v>
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G202" s="3" t="inlineStr">
@@ -14437,30 +14438,30 @@
     <row r="203">
       <c r="A203" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D203" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E203" s="4" t="n">
-        <v>1393</v>
+        <v>1697</v>
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G203" s="3" t="inlineStr">
@@ -14507,30 +14508,30 @@
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E204" s="4" t="n">
-        <v>1393</v>
+        <v>1689</v>
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G204" s="3" t="inlineStr">
@@ -14577,30 +14578,30 @@
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D205" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E205" s="4" t="n">
-        <v>1393</v>
+        <v>1697</v>
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G205" s="3" t="inlineStr">
@@ -14647,30 +14648,30 @@
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D206" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E206" s="4" t="n">
-        <v>1393</v>
+        <v>1689</v>
       </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G206" s="3" t="inlineStr">
@@ -14717,46 +14718,42 @@
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D207" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E207" s="4" t="n">
-        <v>1393</v>
+        <v>1626</v>
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H207" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I207" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="H207" s="5" t="n">
+        <v>49100000</v>
+      </c>
+      <c r="I207" s="5" t="n">
+        <v>30197</v>
       </c>
       <c r="J207" s="3" t="inlineStr">
         <is>
@@ -14787,30 +14784,30 @@
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D208" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E208" s="4" t="n">
-        <v>1393</v>
+        <v>1689</v>
       </c>
       <c r="F208" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G208" s="3" t="inlineStr">
@@ -14857,46 +14854,42 @@
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D209" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E209" s="4" t="n">
-        <v>1393</v>
+        <v>1626</v>
       </c>
       <c r="F209" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H209" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I209" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="H209" s="5" t="n">
+        <v>47679924</v>
+      </c>
+      <c r="I209" s="5" t="n">
+        <v>29323</v>
       </c>
       <c r="J209" s="3" t="inlineStr">
         <is>
@@ -14927,30 +14920,30 @@
     <row r="210">
       <c r="A210" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E210" s="4" t="n">
-        <v>1393</v>
+        <v>1689</v>
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G210" s="3" t="inlineStr">
@@ -14997,46 +14990,42 @@
     <row r="211">
       <c r="A211" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D211" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E211" s="4" t="n">
-        <v>1393</v>
+        <v>1626</v>
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H211" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I211" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="H211" s="5" t="n">
+        <v>47679924</v>
+      </c>
+      <c r="I211" s="5" t="n">
+        <v>29323</v>
       </c>
       <c r="J211" s="3" t="inlineStr">
         <is>
@@ -15067,30 +15056,30 @@
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D212" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E212" s="4" t="n">
-        <v>1393</v>
+        <v>1689</v>
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G212" s="3" t="inlineStr">
@@ -15137,46 +15126,42 @@
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C213" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D213" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E213" s="4" t="n">
-        <v>1393</v>
+        <v>1626</v>
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H213" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I213" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="H213" s="5" t="n">
+        <v>43782600</v>
+      </c>
+      <c r="I213" s="5" t="n">
+        <v>26927</v>
       </c>
       <c r="J213" s="3" t="inlineStr">
         <is>
@@ -15207,30 +15192,30 @@
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D214" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E214" s="4" t="n">
-        <v>1393</v>
+        <v>1689</v>
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G214" s="3" t="inlineStr">
@@ -15277,17 +15262,17 @@
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D215" s="3" t="inlineStr">
@@ -15296,7 +15281,7 @@
         </is>
       </c>
       <c r="E215" s="4" t="n">
-        <v>1393</v>
+        <v>1697</v>
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
@@ -15347,46 +15332,42 @@
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D216" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E216" s="4" t="n">
-        <v>1393</v>
+        <v>1619</v>
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H216" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I216" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="H216" s="5" t="n">
+        <v>42056100</v>
+      </c>
+      <c r="I216" s="5" t="n">
+        <v>25977</v>
       </c>
       <c r="J216" s="3" t="inlineStr">
         <is>
@@ -15417,46 +15398,42 @@
     <row r="217">
       <c r="A217" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D217" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E217" s="4" t="n">
-        <v>1393</v>
+        <v>1626</v>
       </c>
       <c r="F217" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H217" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I217" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="H217" s="5" t="n">
+        <v>42425000</v>
+      </c>
+      <c r="I217" s="5" t="n">
+        <v>26092</v>
       </c>
       <c r="J217" s="3" t="inlineStr">
         <is>
@@ -15487,46 +15464,42 @@
     <row r="218">
       <c r="A218" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D218" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E218" s="4" t="n">
-        <v>1393</v>
+        <v>1619</v>
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H218" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I218" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="H218" s="5" t="n">
+        <v>41887200</v>
+      </c>
+      <c r="I218" s="5" t="n">
+        <v>25872</v>
       </c>
       <c r="J218" s="3" t="inlineStr">
         <is>
@@ -15557,46 +15530,42 @@
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C219" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D219" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E219" s="4" t="n">
-        <v>1393</v>
+        <v>1626</v>
       </c>
       <c r="F219" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H219" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I219" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="H219" s="5" t="n">
+        <v>42085600</v>
+      </c>
+      <c r="I219" s="5" t="n">
+        <v>25883</v>
       </c>
       <c r="J219" s="3" t="inlineStr">
         <is>
@@ -15627,46 +15596,42 @@
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D220" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E220" s="4" t="n">
-        <v>1393</v>
+        <v>1619</v>
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H220" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I220" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="H220" s="5" t="n">
+        <v>45042700</v>
+      </c>
+      <c r="I220" s="5" t="n">
+        <v>27821</v>
       </c>
       <c r="J220" s="3" t="inlineStr">
         <is>
@@ -15697,46 +15662,42 @@
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C221" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D221" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E221" s="4" t="n">
-        <v>1393</v>
+        <v>1626</v>
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H221" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I221" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="H221" s="5" t="n">
+        <v>41237100</v>
+      </c>
+      <c r="I221" s="5" t="n">
+        <v>25361</v>
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
@@ -15767,46 +15728,42 @@
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D222" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E222" s="4" t="n">
-        <v>1393</v>
+        <v>1619</v>
       </c>
       <c r="F222" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H222" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I222" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="H222" s="5" t="n">
+        <v>41718300</v>
+      </c>
+      <c r="I222" s="5" t="n">
+        <v>25768</v>
       </c>
       <c r="J222" s="3" t="inlineStr">
         <is>
@@ -15837,46 +15794,42 @@
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C223" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D223" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E223" s="4" t="n">
-        <v>1393</v>
+        <v>1626</v>
       </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H223" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I223" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="H223" s="5" t="n">
+        <v>45915900</v>
+      </c>
+      <c r="I223" s="5" t="n">
+        <v>28239</v>
       </c>
       <c r="J223" s="3" t="inlineStr">
         <is>
@@ -15907,46 +15860,42 @@
     <row r="224">
       <c r="A224" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D224" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E224" s="4" t="n">
-        <v>1393</v>
+        <v>1619</v>
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H224" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I224" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="H224" s="5" t="n">
+        <v>41550000</v>
+      </c>
+      <c r="I224" s="5" t="n">
+        <v>25664</v>
       </c>
       <c r="J224" s="3" t="inlineStr">
         <is>
@@ -15977,46 +15926,42 @@
     <row r="225">
       <c r="A225" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D225" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E225" s="4" t="n">
-        <v>1393</v>
+        <v>1626</v>
       </c>
       <c r="F225" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H225" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I225" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="H225" s="5" t="n">
+        <v>41576500</v>
+      </c>
+      <c r="I225" s="5" t="n">
+        <v>25570</v>
       </c>
       <c r="J225" s="3" t="inlineStr">
         <is>
@@ -16047,46 +15992,42 @@
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D226" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E226" s="4" t="n">
-        <v>1393</v>
+        <v>1619</v>
       </c>
       <c r="F226" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H226" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I226" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="H226" s="5" t="n">
+        <v>42380000</v>
+      </c>
+      <c r="I226" s="5" t="n">
+        <v>26177</v>
       </c>
       <c r="J226" s="3" t="inlineStr">
         <is>
@@ -16117,46 +16058,42 @@
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C227" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D227" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E227" s="4" t="n">
-        <v>1393</v>
+        <v>1626</v>
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H227" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I227" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="H227" s="5" t="n">
+        <v>42000000</v>
+      </c>
+      <c r="I227" s="5" t="n">
+        <v>25830</v>
       </c>
       <c r="J227" s="3" t="inlineStr">
         <is>
@@ -16187,46 +16124,42 @@
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C228" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D228" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E228" s="4" t="n">
-        <v>1393</v>
+        <v>1619</v>
       </c>
       <c r="F228" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H228" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I228" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="H228" s="5" t="n">
+        <v>42000000</v>
+      </c>
+      <c r="I228" s="5" t="n">
+        <v>25942</v>
       </c>
       <c r="J228" s="3" t="inlineStr">
         <is>
@@ -16257,46 +16190,42 @@
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C229" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D229" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E229" s="4" t="n">
-        <v>1393</v>
+        <v>1626</v>
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H229" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I229" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="H229" s="5" t="n">
+        <v>41576500</v>
+      </c>
+      <c r="I229" s="5" t="n">
+        <v>25570</v>
       </c>
       <c r="J229" s="3" t="inlineStr">
         <is>
@@ -16327,46 +16256,42 @@
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D230" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E230" s="4" t="n">
-        <v>1393</v>
+        <v>1619</v>
       </c>
       <c r="F230" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H230" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I230" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="H230" s="5" t="n">
+        <v>43162395</v>
+      </c>
+      <c r="I230" s="5" t="n">
+        <v>26660</v>
       </c>
       <c r="J230" s="3" t="inlineStr">
         <is>
@@ -16397,46 +16322,42 @@
     <row r="231">
       <c r="A231" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C231" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D231" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E231" s="4" t="n">
-        <v>1393</v>
+        <v>1626</v>
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H231" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I231" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="H231" s="5" t="n">
+        <v>41406800</v>
+      </c>
+      <c r="I231" s="5" t="n">
+        <v>25465</v>
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
@@ -16467,46 +16388,42 @@
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D232" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E232" s="4" t="n">
-        <v>1393</v>
+        <v>1619</v>
       </c>
       <c r="F232" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H232" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I232" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="H232" s="5" t="n">
+        <v>41500000</v>
+      </c>
+      <c r="I232" s="5" t="n">
+        <v>25633</v>
       </c>
       <c r="J232" s="3" t="inlineStr">
         <is>
@@ -16537,46 +16454,42 @@
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C233" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D233" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E233" s="4" t="n">
-        <v>1393</v>
+        <v>1626</v>
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H233" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I233" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="H233" s="5" t="n">
+        <v>45228000</v>
+      </c>
+      <c r="I233" s="5" t="n">
+        <v>27815</v>
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
@@ -16607,46 +16520,42 @@
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C234" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D234" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E234" s="4" t="n">
-        <v>1393</v>
+        <v>1619</v>
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H234" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I234" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="H234" s="5" t="n">
+        <v>47500195</v>
+      </c>
+      <c r="I234" s="5" t="n">
+        <v>29339</v>
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
@@ -16677,46 +16586,42 @@
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C235" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D235" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E235" s="4" t="n">
-        <v>1393</v>
+        <v>1626</v>
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H235" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I235" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="H235" s="5" t="n">
+        <v>41627410</v>
+      </c>
+      <c r="I235" s="5" t="n">
+        <v>25601</v>
       </c>
       <c r="J235" s="3" t="inlineStr">
         <is>
@@ -16747,46 +16652,42 @@
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C236" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D236" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E236" s="4" t="n">
-        <v>1393</v>
+        <v>1619</v>
       </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H236" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I236" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="H236" s="5" t="n">
+        <v>42731700</v>
+      </c>
+      <c r="I236" s="5" t="n">
+        <v>26394</v>
       </c>
       <c r="J236" s="3" t="inlineStr">
         <is>
@@ -16817,46 +16718,42 @@
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C237" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D237" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E237" s="4" t="n">
-        <v>1393</v>
+        <v>1626</v>
       </c>
       <c r="F237" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H237" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I237" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="H237" s="5" t="n">
+        <v>42085600</v>
+      </c>
+      <c r="I237" s="5" t="n">
+        <v>25883</v>
       </c>
       <c r="J237" s="3" t="inlineStr">
         <is>
@@ -16887,46 +16784,42 @@
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C238" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D238" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E238" s="4" t="n">
-        <v>1393</v>
+        <v>1619</v>
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H238" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I238" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="H238" s="5" t="n">
+        <v>49500000</v>
+      </c>
+      <c r="I238" s="5" t="n">
+        <v>30574</v>
       </c>
       <c r="J238" s="3" t="inlineStr">
         <is>
@@ -16957,46 +16850,42 @@
     <row r="239">
       <c r="A239" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D239" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E239" s="4" t="n">
-        <v>1393</v>
+        <v>1626</v>
       </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H239" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I239" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="H239" s="5" t="n">
+        <v>43273500</v>
+      </c>
+      <c r="I239" s="5" t="n">
+        <v>26613</v>
       </c>
       <c r="J239" s="3" t="inlineStr">
         <is>
@@ -17027,26 +16916,26 @@
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D240" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E240" s="4" t="n">
-        <v>1393</v>
+        <v>1689</v>
       </c>
       <c r="F240" s="3" t="inlineStr">
         <is>
@@ -17097,26 +16986,26 @@
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D241" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E241" s="4" t="n">
-        <v>1393</v>
+        <v>1697</v>
       </c>
       <c r="F241" s="3" t="inlineStr">
         <is>
@@ -17172,12 +17061,12 @@
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D242" s="3" t="inlineStr">
@@ -17242,12 +17131,12 @@
       </c>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D243" s="3" t="inlineStr">
@@ -17312,12 +17201,12 @@
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C244" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D244" s="3" t="inlineStr">
@@ -17382,12 +17271,12 @@
       </c>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C245" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D245" s="3" t="inlineStr">
@@ -17396,7 +17285,7 @@
         </is>
       </c>
       <c r="E245" s="4" t="n">
-        <v>1340</v>
+        <v>1393</v>
       </c>
       <c r="F245" s="3" t="inlineStr">
         <is>
@@ -17452,63 +17341,3633 @@
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C246" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D246" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E246" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F246" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G246" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H246" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I246" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J246" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K246" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L246" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M246" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N246" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B247" s="3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C247" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D247" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E247" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F247" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G247" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H247" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I247" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J247" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K247" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L247" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M247" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N247" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B248" s="3" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C248" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D248" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E248" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F248" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G248" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H248" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I248" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J248" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K248" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L248" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M248" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N248" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B249" s="3" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C249" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D249" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E249" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F249" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G249" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H249" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I249" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J249" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K249" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L249" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M249" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N249" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B250" s="3" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C250" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D250" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E250" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F250" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G250" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H250" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I250" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J250" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K250" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L250" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M250" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N250" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B251" s="3" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C251" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D251" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E251" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F251" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G251" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H251" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I251" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J251" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K251" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L251" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M251" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N251" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B252" s="3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C252" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D252" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E252" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F252" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G252" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H252" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I252" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J252" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K252" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L252" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M252" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N252" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B253" s="3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C253" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D253" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E253" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F253" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G253" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H253" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I253" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J253" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K253" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L253" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M253" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N253" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B254" s="3" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C254" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D254" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E254" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F254" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G254" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H254" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I254" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J254" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K254" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L254" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M254" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N254" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B255" s="3" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C255" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D255" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E255" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F255" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G255" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H255" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I255" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J255" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K255" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L255" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M255" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N255" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B256" s="3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C256" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D256" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E256" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F256" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G256" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H256" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I256" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J256" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K256" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L256" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M256" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N256" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B257" s="3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C257" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D257" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E257" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F257" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G257" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H257" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I257" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J257" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K257" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L257" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M257" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N257" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B258" s="3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C258" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D258" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E258" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F258" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G258" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H258" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I258" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J258" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K258" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L258" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M258" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N258" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B259" s="3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C259" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D259" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E259" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F259" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G259" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H259" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I259" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J259" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K259" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L259" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M259" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N259" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B260" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C260" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D260" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E260" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F260" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G260" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H260" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I260" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J260" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K260" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L260" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M260" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N260" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B261" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C261" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D261" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E261" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F261" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G261" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H261" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I261" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J261" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K261" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L261" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M261" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N261" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B262" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C262" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D262" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E262" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F262" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G262" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H262" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I262" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J262" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K262" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L262" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M262" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N262" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B263" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C263" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D263" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E263" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F263" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G263" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H263" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I263" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J263" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K263" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L263" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M263" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N263" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B264" s="3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C264" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D264" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E264" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F264" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G264" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H264" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I264" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J264" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K264" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L264" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M264" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N264" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B265" s="3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C265" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D265" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E265" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F265" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G265" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H265" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I265" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J265" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K265" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L265" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M265" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N265" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B266" s="3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C266" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D266" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E266" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F266" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G266" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H266" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I266" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J266" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K266" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L266" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M266" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N266" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B267" s="3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C267" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D267" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E267" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F267" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G267" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H267" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I267" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J267" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K267" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L267" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M267" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N267" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B268" s="3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C268" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D268" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E268" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F268" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G268" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H268" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I268" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J268" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K268" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L268" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M268" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N268" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B269" s="3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C269" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D269" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E269" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F269" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G269" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H269" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I269" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J269" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K269" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L269" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M269" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N269" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B270" s="3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C270" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D270" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E270" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F270" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G270" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H270" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I270" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J270" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K270" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L270" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M270" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N270" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B271" s="3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C271" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D271" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E271" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F271" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G271" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H271" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I271" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J271" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K271" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L271" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M271" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N271" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B272" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C272" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D272" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E272" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F272" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G272" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H272" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I272" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J272" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K272" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L272" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M272" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N272" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B273" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C273" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D273" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E273" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F273" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G273" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H273" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I273" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J273" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K273" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L273" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M273" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N273" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B274" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C274" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D274" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E274" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F274" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G274" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H274" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I274" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J274" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K274" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L274" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M274" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N274" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B275" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C275" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D275" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E275" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F275" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G275" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H275" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I275" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J275" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K275" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L275" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M275" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N275" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B276" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C276" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D276" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E276" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F276" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G276" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H276" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I276" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J276" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K276" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L276" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M276" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N276" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B277" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C277" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D277" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E277" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F277" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G277" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H277" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I277" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J277" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K277" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L277" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M277" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N277" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B278" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C278" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D278" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E278" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F278" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G278" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H278" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I278" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J278" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K278" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L278" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M278" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N278" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B279" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C279" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D279" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E279" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F279" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G279" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H279" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I279" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J279" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K279" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L279" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M279" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N279" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B280" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C280" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D280" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E280" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F280" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G280" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H280" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I280" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J280" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K280" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L280" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M280" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N280" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B281" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C281" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D281" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E281" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F281" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G281" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H281" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I281" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J281" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K281" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L281" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M281" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N281" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B282" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C282" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D282" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E282" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F282" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G282" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H282" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I282" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J282" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K282" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L282" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M282" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N282" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B283" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C283" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D283" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E283" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F283" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G283" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H283" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I283" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J283" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K283" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L283" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M283" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N283" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B284" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C284" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D284" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E284" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F284" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G284" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H284" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I284" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J284" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K284" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L284" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M284" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N284" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B285" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C285" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D285" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E285" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F285" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G285" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H285" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I285" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J285" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K285" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L285" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M285" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N285" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B286" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C286" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D286" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E286" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F286" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G286" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H286" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I286" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J286" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K286" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L286" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M286" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N286" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B287" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C287" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D287" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E287" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F287" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G287" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H287" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I287" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J287" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K287" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L287" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M287" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N287" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B288" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C288" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D288" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E288" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F288" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G288" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H288" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I288" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J288" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K288" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L288" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M288" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N288" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B289" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C289" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D289" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E289" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F289" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G289" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H289" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I289" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J289" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K289" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L289" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M289" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N289" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B290" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C290" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D290" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E290" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F290" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G290" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H290" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I290" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J290" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K290" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L290" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M290" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N290" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B291" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C291" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D291" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E291" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F291" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G291" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H291" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I291" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J291" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K291" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L291" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M291" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N291" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B292" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C292" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D292" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E292" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F292" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G292" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H292" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I292" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J292" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K292" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L292" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M292" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N292" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B293" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C293" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D293" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E293" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F293" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G293" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H293" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I293" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J293" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K293" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L293" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M293" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N293" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B294" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C294" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D294" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E294" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F294" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G294" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H294" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I294" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J294" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K294" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L294" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M294" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N294" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B295" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C295" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D295" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E295" s="4" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F295" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G295" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H295" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I295" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J295" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K295" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L295" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M295" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N295" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B296" s="3" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C246" s="3" t="inlineStr">
+      <c r="C296" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D296" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E296" s="4" t="n">
+        <v>1340</v>
+      </c>
+      <c r="F296" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G296" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H296" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I296" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J296" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K296" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L296" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M296" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N296" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="3" t="inlineStr">
+        <is>
+          <t>8座</t>
+        </is>
+      </c>
+      <c r="B297" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C297" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D246" s="3" t="inlineStr">
+      <c r="D297" s="3" t="inlineStr">
         <is>
           <t>3房</t>
         </is>
       </c>
-      <c r="E246" s="4" t="n">
+      <c r="E297" s="4" t="n">
         <v>1340</v>
       </c>
-      <c r="F246" s="3" t="inlineStr">
+      <c r="F297" s="3" t="inlineStr">
         <is>
           <t>待售</t>
         </is>
       </c>
-      <c r="G246" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H246" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I246" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J246" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K246" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L246" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M246" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N246" s="3" t="inlineStr">
+      <c r="G297" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H297" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I297" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J297" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K297" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L297" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M297" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N297" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -17737,7 +21196,7 @@
           <t>A | 1864呎 (4+房)
 $6080万
 $32,618/呎
-(25年-09月)</t>
+(25年-09月-01日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -17760,7 +21219,7 @@
           <t>A | 1864呎 (4+房)
 $5525万
 $29,642/呎
-(25年-09月)</t>
+(25年-09月-15日)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -17768,7 +21227,7 @@
           <t>B | 2107呎 (4+房)
 $6572万
 $31,191/呎
-(25年-09月)</t>
+(25年-09月-10日)</t>
         </is>
       </c>
     </row>
@@ -17783,7 +21242,7 @@
           <t>A | 1864呎 (4+房)
 $5940万
 $31,866/呎
-(25年-07月)</t>
+(25年-07月-10日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -17814,7 +21273,7 @@
           <t>B | 2107呎 (4+房)
 $6900万
 $32,748/呎
-(24年-08月)</t>
+(24年-08月-20日)</t>
         </is>
       </c>
     </row>
@@ -17829,7 +21288,7 @@
           <t>A | 1864呎 (4+房)
 $5408万
 $29,013/呎
-(25年-07月)</t>
+(25年-07月-10日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -17837,7 +21296,7 @@
           <t>B | 2107呎 (4+房)
 $6600万
 $31,324/呎
-(24年-10月)</t>
+(24年-10月-15日)</t>
         </is>
       </c>
     </row>
@@ -17852,7 +21311,7 @@
           <t>A | 1864呎 (4+房)
 $5800万
 $31,116/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -17860,7 +21319,7 @@
           <t>B | 2107呎 (4+房)
 $6792万
 $32,234/呎
-(25年-07月)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
     </row>
@@ -17875,7 +21334,7 @@
           <t>A | 1864呎 (4+房)
 $5238万
 $28,101/呎
-(24年-10月)</t>
+(24年-10月-15日)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -17883,7 +21342,7 @@
           <t>B | 2107呎 (4+房)
 $6608万
 $31,362/呎
-(24年-09月)</t>
+(24年-09月-09日)</t>
         </is>
       </c>
     </row>
@@ -17898,7 +21357,7 @@
           <t>A | 1864呎 (4+房)
 $5183万
 $27,808/呎
-(24年-07月)</t>
+(24年-07月-16日)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -17906,7 +21365,7 @@
           <t>B | 2107呎 (4+房)
 $6446万
 $30,591/呎
-(24年-07月)</t>
+(24年-07月-11日)</t>
         </is>
       </c>
     </row>
@@ -17921,7 +21380,7 @@
           <t>A | 1864呎 (4+房)
 $5561万
 $29,835/呎
-(24年-06月)</t>
+(24年-06月-11日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -17929,7 +21388,7 @@
           <t>B | 2108呎 (4+房)
 $6189万
 $29,358/呎
-(24年-07月)</t>
+(24年-07月-03日)</t>
         </is>
       </c>
     </row>
@@ -17944,7 +21403,7 @@
           <t>A | 1864呎 (4+房)
 $5548万
 $29,765/呎
-(24年-05月)</t>
+(24年-05月-15日)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -17952,7 +21411,7 @@
           <t>B | 2108呎 (4+房)
 $6287万
 $29,825/呎
-(24年-05月)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
     </row>
@@ -17967,7 +21426,7 @@
           <t>A | 1864呎 (4+房)
 $5086万
 $27,283/呎
-(24年-05月)</t>
+(24年-05月-15日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -17975,7 +21434,7 @@
           <t>B | 2108呎 (4+房)
 $5865万
 $27,821/呎
-(24年-05月)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
     </row>
@@ -17990,7 +21449,7 @@
           <t>A | 1864呎 (4+房)
 $5526万
 $29,645/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -17998,7 +21457,7 @@
           <t>B | 2108呎 (4+房)
 $5865万
 $27,821/呎
-(24年-05月)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
     </row>
@@ -18013,7 +21472,7 @@
           <t>A | 1864呎 (4+房)
 $5546万
 $29,756/呎
-(24年-05月)</t>
+(24年-05月-15日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -18021,7 +21480,7 @@
           <t>B | 2108呎 (4+房)
 $6297万
 $29,873/呎
-(24年-05月)</t>
+(24年-05月-15日)</t>
         </is>
       </c>
     </row>
@@ -18036,7 +21495,7 @@
           <t>A | 1864呎 (4+房)
 $5546万
 $29,756/呎
-(24年-05月)</t>
+(24年-05月-15日)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -18044,7 +21503,7 @@
           <t>B | 2108呎 (4+房)
 $6297万
 $29,873/呎
-(24年-05月)</t>
+(24年-05月-15日)</t>
         </is>
       </c>
     </row>
@@ -18059,7 +21518,7 @@
           <t>A | 1864呎 (4+房)
 $5178万
 $27,778/呎
-(24年-05月)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -18067,7 +21526,7 @@
           <t>B | 2108呎 (4+房)
 $6448万
 $30,588/呎
-(24年-05月)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
     </row>
@@ -18082,7 +21541,7 @@
           <t>A | 1864呎 (4+房)
 $4920万
 $26,395/呎
-(24年-07月)</t>
+(24年-07月-11日)</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
@@ -18090,7 +21549,7 @@
           <t>B | 2108呎 (4+房)
 $6455万
 $30,619/呎
-(24年-05月)</t>
+(24年-05月-15日)</t>
         </is>
       </c>
     </row>
@@ -18105,7 +21564,7 @@
           <t>A | 1864呎 (4+房)
 $5250万
 $28,165/呎
-(25年-02月)</t>
+(25年-02月-19日)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -18113,7 +21572,7 @@
           <t>B | 2108呎 (4+房)
 $6046万
 $28,682/呎
-(24年-09月)</t>
+(24年-09月-24日)</t>
         </is>
       </c>
     </row>
@@ -18128,7 +21587,7 @@
           <t>A | 1864呎 (4+房)
 $5380万
 $28,863/呎
-(26年-01月)</t>
+(26年-01月-28日)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
@@ -18136,7 +21595,7 @@
           <t>B | 2108呎 (4+房)
 $5540万
 $26,281/呎
-(25年-01月)</t>
+(25年-01月-12日)</t>
         </is>
       </c>
     </row>
@@ -18432,7 +21891,7 @@
           <t>A | 2137呎 (4+房)
 $7094万
 $33,196/呎
-(25年-10月)</t>
+(25年-10月-22日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -18440,7 +21899,7 @@
           <t>B | 2464呎 (4+房)
 $8494万
 $34,472/呎
-(25年-10月)</t>
+(25年-10月-22日)</t>
         </is>
       </c>
     </row>
@@ -18463,7 +21922,7 @@
           <t>B | 2464呎 (4+房)
 $7994万
 $32,444/呎
-(25年-10月)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
     </row>
@@ -18478,7 +21937,7 @@
           <t>A | 2137呎 (4+房)
 $6582万
 $30,799/呎
-(25年-10月)</t>
+(25年-10月-21日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -18486,7 +21945,7 @@
           <t>B | 2464呎 (4+房)
 $8200万
 $33,279/呎
-(25年-08月)</t>
+(25年-08月-03日)</t>
         </is>
       </c>
     </row>
@@ -18509,7 +21968,7 @@
           <t>B | 2464呎 (4+房)
 $8200万
 $33,279/呎
-(25年-08月)</t>
+(25年-08月-03日)</t>
         </is>
       </c>
     </row>
@@ -18524,7 +21983,7 @@
           <t>A | 2137呎 (4+房)
 $6526万
 $30,540/呎
-(25年-04月)</t>
+(25年-04月-16日)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -18532,7 +21991,7 @@
           <t>B | 2464呎 (4+房)
 $8101万
 $32,876/呎
-(25年-04月)</t>
+(25年-04月-16日)</t>
         </is>
       </c>
     </row>
@@ -18547,7 +22006,7 @@
           <t>A | 2137呎 (4+房)
 $6526万
 $30,540/呎
-(25年-04月)</t>
+(25年-04月-16日)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -18555,7 +22014,7 @@
           <t>B | 2464呎 (4+房)
 $8101万
 $32,876/呎
-(25年-04月)</t>
+(25年-04月-16日)</t>
         </is>
       </c>
     </row>
@@ -18570,7 +22029,7 @@
           <t>A | 2137呎 (4+房)
 $6526万
 $30,540/呎
-(25年-04月)</t>
+(25年-04月-16日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -18578,7 +22037,7 @@
           <t>B | 2604呎 (4+房)
 $8101万
 $31,108/呎
-(25年-04月)</t>
+(25年-04月-16日)</t>
         </is>
       </c>
     </row>
@@ -18601,7 +22060,7 @@
           <t>B | 2464呎 (4+房)
 $8333万
 $33,818/呎
-(25年-01月)</t>
+(25年-01月-21日)</t>
         </is>
       </c>
     </row>
@@ -18624,7 +22083,7 @@
           <t>B | 2464呎 (4+房)
 $8122万
 $32,961/呎
-(25年-05月)</t>
+(25年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -18639,7 +22098,7 @@
           <t>A | 2137呎 (4+房)
 $6525万
 $30,536/呎
-(25年-02月)</t>
+(25年-02月-16日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -18647,7 +22106,7 @@
           <t>B | 2464呎 (4+房)
 $8075万
 $32,770/呎
-(25年-02月)</t>
+(25年-02月-17日)</t>
         </is>
       </c>
     </row>
@@ -18662,7 +22121,7 @@
           <t>A | 2137呎 (4+房)
 $6478万
 $30,314/呎
-(25年-09月)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -18670,7 +22129,7 @@
           <t>B | 2464呎 (4+房)
 $7900万
 $32,062/呎
-(24年-12月)</t>
+(24年-12月-03日)</t>
         </is>
       </c>
     </row>
@@ -18685,7 +22144,7 @@
           <t>A | 2137呎 (4+房)
 $7163万
 $33,520/呎
-(25年-12月)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -18693,7 +22152,7 @@
           <t>B | 2464呎 (4+房)
 $7900万
 $32,062/呎
-(24年-12月)</t>
+(24年-12月-03日)</t>
         </is>
       </c>
     </row>
@@ -18716,7 +22175,7 @@
           <t>B | 2464呎 (4+房)
 $8100万
 $32,873/呎
-(25年-06月)</t>
+(25年-06月-02日)</t>
         </is>
       </c>
     </row>
@@ -18739,7 +22198,7 @@
           <t>B | 2464呎 (4+房)
 $7853万
 $31,870/呎
-(25年-01月)</t>
+(25年-01月-14日)</t>
         </is>
       </c>
     </row>
@@ -18754,7 +22213,7 @@
           <t>A | 2137呎 (4+房)
 $7096万
 $33,206/呎
-(25年-12月)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -18762,7 +22221,7 @@
           <t>B | 2464呎 (4+房)
 $8251万
 $33,485/呎
-(25年-12月)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
     </row>
@@ -18777,7 +22236,7 @@
           <t>A | 2137呎 (4+房)
 $6723万
 $31,461/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
@@ -18785,7 +22244,7 @@
           <t>B | 2464呎 (4+房)
 $7830万
 $31,776/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
     </row>
@@ -19043,7 +22502,7 @@
           <t>B | 3635呎 (4+房)
 $18466万
 $50,800/呎
-(23年-05月)</t>
+(23年-05月-18日)</t>
         </is>
       </c>
     </row>
@@ -19296,7 +22755,7 @@
           <t>B | 3627呎 (4+房)
 $18328万
 $50,531/呎
-(23年-02月)</t>
+(23年-02月-13日)</t>
         </is>
       </c>
     </row>
@@ -19311,7 +22770,7 @@
           <t>A | 3207呎 (4+房)
 $16417万
 $51,191/呎
-(23年-01月)</t>
+(23年-01月-26日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -19319,7 +22778,7 @@
           <t>B | 3477呎 (4+房)
 $14008万
 $40,288/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
     </row>
@@ -19342,7 +22801,7 @@
           <t>B | 3477呎 (4+房)
 $17228万
 $49,549/呎
-(23年-12月)</t>
+(23年-12月-14日)</t>
         </is>
       </c>
     </row>
@@ -19357,7 +22816,7 @@
           <t>A | 3207呎 (4+房)
 $12106万
 $37,749/呎
-(24年-07月)</t>
+(24年-07月-17日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -19365,7 +22824,7 @@
           <t>B | 3627呎 (4+房)
 $13194万
 $36,379/呎
-(24年-07月)</t>
+(24年-07月-17日)</t>
         </is>
       </c>
     </row>
@@ -19403,7 +22862,7 @@
           <t>A | 3207呎 (4+房)
 $12066万
 $37,625/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
@@ -19761,7 +23220,7 @@
           <t>B | 1824呎 (4+房)
 $7582万
 $41,566/呎
-(24年-01月)</t>
+(24年-01月-21日)</t>
         </is>
       </c>
     </row>
@@ -19914,7 +23373,7 @@
           <t>A | 2178呎 (4+房)
 $7339万
 $33,695/呎
-(25年-10月)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -19960,7 +23419,7 @@
           <t>A | 2178呎 (4+房)
 $6745万
 $30,970/呎
-(25年-08月)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -19983,7 +23442,7 @@
           <t>A | 2178呎 (4+房)
 $7251万
 $33,290/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -20006,7 +23465,7 @@
           <t>A | 2178呎 (4+房)
 $6956万
 $31,937/呎
-(25年-10月)</t>
+(25年-10月-01日)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -20014,7 +23473,7 @@
           <t>B | 1824呎 (4+房)
 $5323万
 $29,181/呎
-(25年-10月)</t>
+(25年-10月-01日)</t>
         </is>
       </c>
     </row>
@@ -20029,7 +23488,7 @@
           <t>A | 2178呎 (4+房)
 $6468万
 $29,697/呎
-(24年-07月)</t>
+(24年-07月-03日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -20037,7 +23496,7 @@
           <t>B | 1824呎 (4+房)
 $5800万
 $31,798/呎
-(24年-05月)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
     </row>
@@ -20052,7 +23511,7 @@
           <t>A | 2178呎 (4+房)
 $6280万
 $28,834/呎
-(25年-07月)</t>
+(25年-07月-28日)</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
@@ -20060,7 +23519,7 @@
           <t>B | 1944呎 (4+房)
 $6318万
 $32,500/呎
-(26年-07月)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
     </row>
@@ -20083,7 +23542,7 @@
           <t>B | 1824呎 (4+房)
 $5724万
 $31,379/呎
-(26年-02月)</t>
+(26年-02月-01日)</t>
         </is>
       </c>
     </row>
@@ -20106,7 +23565,7 @@
           <t>B | 1824呎 (4+房)
 $5953万
 $32,634/呎
-(26年-06月)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
     </row>
@@ -20129,7 +23588,7 @@
           <t>B | 1824呎 (4+房)
 $5724万
 $31,379/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
     </row>
@@ -20171,6 +23630,708 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:F30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>6座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 3184呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 1696呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 1689呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 1696呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 1689呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 1697呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 1689呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 1697呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 1689呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 1697呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 1689呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 1697呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 1689呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 1697呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 1689呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>A | 1626呎 (4+房)
+$4910万
+$30,197/呎
+(25年-09月-14日)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 1689呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>A | 1626呎 (4+房)
+$4768万
+$29,323/呎
+(25年-05月-28日)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 1689呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>A | 1626呎 (4+房)
+$4768万
+$29,323/呎
+(25年-06月-01日)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 1689呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>A | 1626呎 (4+房)
+$4378万
+$26,927/呎
+(25年-06月-18日)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 1689呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 1697呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 1689呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>A | 1626呎 (4+房)
+$4242万
+$26,092/呎
+(25年-05月-14日)</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>B | 1619呎 (4+房)
+$4206万
+$25,977/呎
+(25年-07月-01日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>A | 1626呎 (4+房)
+$4209万
+$25,883/呎
+(25年-05月-07日)</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>B | 1619呎 (4+房)
+$4189万
+$25,872/呎
+(25年-06月-02日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>A | 1626呎 (4+房)
+$4124万
+$25,361/呎
+(24年-06月-27日)</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>B | 1619呎 (4+房)
+$4504万
+$27,821/呎
+(24年-06月-27日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>A | 1626呎 (4+房)
+$4592万
+$28,239/呎
+(24年-11月-06日)</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>B | 1619呎 (4+房)
+$4172万
+$25,768/呎
+(25年-02月-18日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>A | 1626呎 (4+房)
+$4158万
+$25,570/呎
+(24年-10月-30日)</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="inlineStr">
+        <is>
+          <t>B | 1619呎 (4+房)
+$4155万
+$25,664/呎
+(24年-11月-10日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>A | 1626呎 (4+房)
+$4200万
+$25,830/呎
+(24年-12月-17日)</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t>B | 1619呎 (4+房)
+$4238万
+$26,177/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>A | 1626呎 (4+房)
+$4158万
+$25,570/呎
+(24年-11月-21日)</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t>B | 1619呎 (4+房)
+$4200万
+$25,942/呎
+(25年-10月-05日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>A | 1626呎 (4+房)
+$4141万
+$25,465/呎
+(24年-07月-16日)</t>
+        </is>
+      </c>
+      <c r="C25" s="23" t="inlineStr">
+        <is>
+          <t>B | 1619呎 (4+房)
+$4316万
+$26,660/呎
+(25年-12月-03日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>A | 1626呎 (4+房)
+$4523万
+$27,815/呎
+(24年-10月-30日)</t>
+        </is>
+      </c>
+      <c r="C26" s="23" t="inlineStr">
+        <is>
+          <t>B | 1619呎 (4+房)
+$4150万
+$25,633/呎
+(25年-10月-29日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>A | 1626呎 (4+房)
+$4163万
+$25,601/呎
+(25年-07月-01日)</t>
+        </is>
+      </c>
+      <c r="C27" s="23" t="inlineStr">
+        <is>
+          <t>B | 1619呎 (4+房)
+$4750万
+$29,339/呎
+(25年-12月-10日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>A | 1626呎 (4+房)
+$4209万
+$25,883/呎
+(25年-05月-29日)</t>
+        </is>
+      </c>
+      <c r="C28" s="23" t="inlineStr">
+        <is>
+          <t>B | 1619呎 (4+房)
+$4273万
+$26,394/呎
+(25年-12月-17日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>A | 1626呎 (4+房)
+$4327万
+$26,613/呎
+(25年-12月-10日)</t>
+        </is>
+      </c>
+      <c r="C29" s="23" t="inlineStr">
+        <is>
+          <t>B | 1619呎 (4+房)
+$4950万
+$30,574/呎
+(26年-02月-09日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>A | 1697呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>B | 1689呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
